--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6840A94E-363C-4286-8512-333E7C90F984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4B4782-80D2-41C9-A814-EBBB82C65607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1563,6 +1563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1587,7 +1588,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1602,7 +1603,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>237</v>
       </c>
@@ -1620,7 +1621,7 @@
         <v>+51 933 668 277</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1638,7 +1639,7 @@
         <v>+51 980 596 555</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1656,7 +1657,7 @@
         <v>+58 424-7086947</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -1671,7 +1672,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>236</v>
       </c>
@@ -1689,7 +1690,7 @@
         <v>+58 412-1322018</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>194</v>
       </c>
@@ -1704,7 +1705,7 @@
         <v>+ 9 7927 3083</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -1719,7 +1720,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1737,7 +1738,7 @@
         <v>+51 985 699 608</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1755,7 +1756,7 @@
         <v>+52 1 56 1007 9583</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>192</v>
       </c>
@@ -1773,7 +1774,7 @@
         <v>+52 1 81 2944 2313</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1788,7 +1789,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1803,7 +1804,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>160</v>
       </c>
@@ -1818,7 +1819,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1836,7 +1837,7 @@
         <v>+51  984 190 584</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>149</v>
       </c>
@@ -1848,7 +1849,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1866,7 +1867,7 @@
         <v>+51 984 267 160</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1884,7 +1885,7 @@
         <v>+51  912 858 811</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -1896,7 +1897,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>136</v>
       </c>
@@ -1914,7 +1915,7 @@
         <v>+51 949 647 819</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1932,7 +1933,7 @@
         <v>+34  646 20 50 99</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>229</v>
       </c>
@@ -1941,7 +1942,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>137</v>
       </c>
@@ -1959,7 +1960,7 @@
         <v>+52  1 222 102 8165</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1977,7 +1978,7 @@
         <v>+58 416-4398466</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -1986,7 +1987,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -2004,7 +2005,7 @@
         <v>+57 322 4761144</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -2019,7 +2020,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>235</v>
       </c>
@@ -2055,7 +2056,7 @@
         <v>+51 933448842</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -2070,7 +2071,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2079,7 +2080,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>180</v>
       </c>
@@ -2097,7 +2098,7 @@
         <v>+51 950 746 501</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -2115,7 +2116,7 @@
         <v>+54 9 3794 73 7373</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>119</v>
       </c>
@@ -2124,7 +2125,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>181</v>
       </c>
@@ -2142,7 +2143,7 @@
         <v>+55 71 9370-7438</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>255</v>
       </c>
@@ -2157,7 +2158,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -2175,7 +2176,7 @@
         <v>+34 601 36 84 69</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2190,7 +2191,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>185</v>
       </c>
@@ -2208,7 +2209,7 @@
         <v>+51  917 057 695</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -2226,7 +2227,7 @@
         <v>+34 608 39 51 22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>222</v>
       </c>
@@ -2241,7 +2242,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>117</v>
       </c>
@@ -2256,7 +2257,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -2271,7 +2272,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>199</v>
       </c>
@@ -2280,7 +2281,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -2289,7 +2290,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>170</v>
       </c>
@@ -2298,7 +2299,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -2307,7 +2308,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2325,7 +2326,7 @@
         <v>+51  920 449 371</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>68</v>
       </c>
@@ -2343,7 +2344,7 @@
         <v>+51  912 209 142</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -2352,7 +2353,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -2370,7 +2371,7 @@
         <v>+505 8799 9543</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>125</v>
       </c>
@@ -2388,7 +2389,7 @@
         <v>+52 1 686 589 5829</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2406,7 +2407,7 @@
         <v>+51 992 067 030</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -2421,7 +2422,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -2436,7 +2437,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>231</v>
       </c>
@@ -2445,7 +2446,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -2463,7 +2464,7 @@
         <v>+58  412-7396859</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -2481,7 +2482,7 @@
         <v>+52 1 921 208 0809</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>100</v>
       </c>
@@ -2496,7 +2497,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>166</v>
       </c>
@@ -2514,7 +2515,7 @@
         <v>+504 3204-1711</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -2523,7 +2524,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>223</v>
       </c>
@@ -2538,7 +2539,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -2556,7 +2557,7 @@
         <v>+1 305 8902347</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>168</v>
       </c>
@@ -2565,7 +2566,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>124</v>
       </c>
@@ -2574,7 +2575,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>177</v>
       </c>
@@ -2583,7 +2584,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>217</v>
       </c>
@@ -2592,7 +2593,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -2610,7 +2611,7 @@
         <v>+506  8936 2350</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>159</v>
       </c>
@@ -2628,7 +2629,7 @@
         <v>+1 (253) 212-8032</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -2643,7 +2644,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>195</v>
       </c>
@@ -2652,7 +2653,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>110</v>
       </c>
@@ -2661,7 +2662,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>188</v>
       </c>
@@ -2670,7 +2671,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>241</v>
       </c>
@@ -2685,7 +2686,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>31</v>
       </c>
@@ -2703,7 +2704,7 @@
         <v>+51  912 058 374</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -2718,7 +2719,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>133</v>
       </c>
@@ -2727,7 +2728,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -2736,7 +2737,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>106</v>
       </c>
@@ -2745,7 +2746,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>215</v>
       </c>
@@ -2763,7 +2764,7 @@
         <v>+593  96 083 0485</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -2772,7 +2773,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
@@ -2781,7 +2782,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -2799,7 +2800,7 @@
         <v>+51  983 379 394</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -2808,7 +2809,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>162</v>
       </c>
@@ -2826,7 +2827,7 @@
         <v>+51 980 679 898</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>230</v>
       </c>
@@ -2841,7 +2842,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>139</v>
       </c>
@@ -2850,7 +2851,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>176</v>
       </c>
@@ -2859,7 +2860,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>122</v>
       </c>
@@ -2874,7 +2875,7 @@
         <v xml:space="preserve">+593 </v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>214</v>
       </c>
@@ -2883,7 +2884,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>45</v>
       </c>
@@ -2901,7 +2902,7 @@
         <v>+54 9 3412 81-3587</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -2916,7 +2917,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>120</v>
       </c>
@@ -2934,7 +2935,7 @@
         <v>+57  302 5578252</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>206</v>
       </c>
@@ -2952,7 +2953,7 @@
         <v>+593 96 151 5565</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>244</v>
       </c>
@@ -2961,7 +2962,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>240</v>
       </c>
@@ -2979,7 +2980,7 @@
         <v>+54 9 11 2783 9968</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>155</v>
       </c>
@@ -2988,7 +2989,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>34</v>
       </c>
@@ -3006,7 +3007,7 @@
         <v>+53 5 1113536</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>140</v>
       </c>
@@ -3021,7 +3022,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>233</v>
       </c>
@@ -3036,7 +3037,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>141</v>
       </c>
@@ -3051,7 +3052,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>55</v>
       </c>
@@ -3069,7 +3070,7 @@
         <v>+1 (809) 658-5500</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>154</v>
       </c>
@@ -3087,7 +3088,7 @@
         <v>+58 424-1216695</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>169</v>
       </c>
@@ -3105,7 +3106,7 @@
         <v>+51 963 745 855</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>225</v>
       </c>
@@ -3114,7 +3115,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -3129,7 +3130,7 @@
         <v>+ 98 768 2900</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -3138,7 +3139,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>247</v>
       </c>
@@ -3147,7 +3148,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>243</v>
       </c>
@@ -3162,7 +3163,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>156</v>
       </c>
@@ -3180,7 +3181,7 @@
         <v>+58 414-4473628</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>43</v>
       </c>
@@ -3189,7 +3190,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>224</v>
       </c>
@@ -3204,7 +3205,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>163</v>
       </c>
@@ -3219,7 +3220,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>56</v>
       </c>
@@ -3228,7 +3229,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>150</v>
       </c>
@@ -3237,7 +3238,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -3255,7 +3256,7 @@
         <v>+51  906 691 465</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3270,7 +3271,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>165</v>
       </c>
@@ -3279,7 +3280,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>46</v>
       </c>
@@ -3288,7 +3289,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>210</v>
       </c>
@@ -3297,7 +3298,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3312,7 +3313,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>21</v>
       </c>
@@ -3330,7 +3331,7 @@
         <v>+51 996 668 615</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>77</v>
       </c>
@@ -3345,7 +3346,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>250</v>
       </c>
@@ -3354,7 +3355,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>193</v>
       </c>
@@ -3363,7 +3364,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>254</v>
       </c>
@@ -3381,7 +3382,7 @@
         <v>+51  921 447 908</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>12</v>
       </c>
@@ -3399,7 +3400,7 @@
         <v>+51 976 413 331</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>184</v>
       </c>
@@ -3414,7 +3415,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>101</v>
       </c>
@@ -3423,7 +3424,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>157</v>
       </c>
@@ -3438,7 +3439,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>47</v>
       </c>
@@ -3453,7 +3454,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>221</v>
       </c>
@@ -3462,7 +3463,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>258</v>
       </c>
@@ -3480,7 +3481,7 @@
         <v>+54 9 11 2526 8333</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>248</v>
       </c>
@@ -3489,7 +3490,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -3507,7 +3508,7 @@
         <v>+52 1 81 2684 3183</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>135</v>
       </c>
@@ -3516,7 +3517,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>179</v>
       </c>
@@ -3531,7 +3532,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>109</v>
       </c>
@@ -3546,7 +3547,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -3555,7 +3556,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>26</v>
       </c>
@@ -3573,7 +3574,7 @@
         <v>+57 302 3773516</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -3591,7 +3592,7 @@
         <v>+54  9 11 2372-2211</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>212</v>
       </c>
@@ -3609,7 +3610,7 @@
         <v>+51 960 749 072</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -3627,7 +3628,7 @@
         <v>+51 984 784 816</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>245</v>
       </c>
@@ -3642,7 +3643,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>208</v>
       </c>
@@ -3651,7 +3652,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>211</v>
       </c>
@@ -3660,7 +3661,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>175</v>
       </c>
@@ -3669,7 +3670,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>186</v>
       </c>
@@ -3684,7 +3685,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>65</v>
       </c>
@@ -3702,7 +3703,7 @@
         <v>+593 98 174 5020</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -3717,7 +3718,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>118</v>
       </c>
@@ -3732,7 +3733,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>173</v>
       </c>
@@ -3750,7 +3751,7 @@
         <v>+52 1 771 297 6010</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>178</v>
       </c>
@@ -3765,7 +3766,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>189</v>
       </c>
@@ -3783,7 +3784,7 @@
         <v>+52  1 983 752 2450</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>93</v>
       </c>
@@ -3798,7 +3799,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>153</v>
       </c>
@@ -3816,7 +3817,7 @@
         <v>+58 424-6956750</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>72</v>
       </c>
@@ -3834,7 +3835,7 @@
         <v>+51  965 337 810</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>86</v>
       </c>
@@ -3849,7 +3850,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>87</v>
       </c>
@@ -3864,7 +3865,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>75</v>
       </c>
@@ -3879,7 +3880,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>201</v>
       </c>
@@ -3894,7 +3895,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>253</v>
       </c>
@@ -3912,7 +3913,7 @@
         <v>+51  945 349 568</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>252</v>
       </c>
@@ -3930,7 +3931,7 @@
         <v>+52 1 735 162 2046</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>246</v>
       </c>
@@ -3948,7 +3949,7 @@
         <v>+51 970 857 085</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>78</v>
       </c>
@@ -3963,7 +3964,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>147</v>
       </c>
@@ -3981,7 +3982,7 @@
         <v>+52  1 673 472 3074</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>59</v>
       </c>
@@ -3999,7 +4000,7 @@
         <v>+54 9 2974 22-6785</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>242</v>
       </c>
@@ -4017,7 +4018,7 @@
         <v>+52 1 55 1805 8456</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>234</v>
       </c>
@@ -4032,7 +4033,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -4050,7 +4051,7 @@
         <v>+54  9 11 6135-9811</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>202</v>
       </c>
@@ -4059,7 +4060,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>219</v>
       </c>
@@ -4077,7 +4078,7 @@
         <v>+51 991 342 085</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>69</v>
       </c>
@@ -4092,7 +4093,7 @@
         <v xml:space="preserve">+506 </v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>218</v>
       </c>
@@ -4107,7 +4108,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>167</v>
       </c>
@@ -4116,7 +4117,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>257</v>
       </c>
@@ -4134,7 +4135,7 @@
         <v>+53 5 6957902</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>134</v>
       </c>
@@ -4143,7 +4144,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>132</v>
       </c>
@@ -4152,7 +4153,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>29</v>
       </c>
@@ -4170,7 +4171,7 @@
         <v>+51 977 404 957</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>53</v>
       </c>
@@ -4188,7 +4189,7 @@
         <v>+52 1 229 229 9515</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>64</v>
       </c>
@@ -4206,7 +4207,7 @@
         <v>+51 986 824 543</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -4224,7 +4225,7 @@
         <v>+591 69865757</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>58</v>
       </c>
@@ -4242,7 +4243,7 @@
         <v>+506  7139 5493</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>115</v>
       </c>
@@ -4257,7 +4258,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>198</v>
       </c>
@@ -4272,7 +4273,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>207</v>
       </c>
@@ -4281,7 +4282,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>3</v>
       </c>
@@ -4299,7 +4300,7 @@
         <v>+51 955 121 011</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>172</v>
       </c>
@@ -4314,7 +4315,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>104</v>
       </c>
@@ -4323,7 +4324,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>152</v>
       </c>
@@ -4332,7 +4333,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>103</v>
       </c>
@@ -4347,7 +4348,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>259</v>
       </c>
@@ -4356,7 +4357,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>80</v>
       </c>
@@ -4371,7 +4372,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>190</v>
       </c>
@@ -4389,7 +4390,7 @@
         <v>+52  1 756 103 6825</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>204</v>
       </c>
@@ -4398,7 +4399,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>174</v>
       </c>
@@ -4413,7 +4414,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>203</v>
       </c>
@@ -4422,7 +4423,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>48</v>
       </c>
@@ -4440,7 +4441,7 @@
         <v>+52 1 231 176 9718</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>249</v>
       </c>
@@ -4449,7 +4450,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>200</v>
       </c>
@@ -4467,7 +4468,7 @@
         <v>+52  1 55 7364 9786</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>151</v>
       </c>
@@ -4476,7 +4477,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>183</v>
       </c>
@@ -4491,7 +4492,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>196</v>
       </c>
@@ -4500,7 +4501,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>96</v>
       </c>
@@ -4509,7 +4510,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>251</v>
       </c>
@@ -4518,7 +4519,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>97</v>
       </c>
@@ -4533,7 +4534,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>28</v>
       </c>
@@ -4551,7 +4552,7 @@
         <v>+51 981 000 049</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>191</v>
       </c>
@@ -4566,7 +4567,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>145</v>
       </c>
@@ -4584,7 +4585,7 @@
         <v>+56 9 7878 6558</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>7</v>
       </c>
@@ -4602,7 +4603,7 @@
         <v>+51 973 614 848</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>15</v>
       </c>
@@ -4620,7 +4621,7 @@
         <v>+51 971 942 638</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>238</v>
       </c>
@@ -4635,7 +4636,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>40</v>
       </c>
@@ -4653,7 +4654,7 @@
         <v>+58 422-0376517</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>91</v>
       </c>
@@ -4668,7 +4669,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>227</v>
       </c>
@@ -4686,7 +4687,7 @@
         <v>+52  1 834 252 9665</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>14</v>
       </c>
@@ -4704,7 +4705,7 @@
         <v>+506 6082 6653</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>67</v>
       </c>
@@ -4713,7 +4714,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>116</v>
       </c>
@@ -4728,7 +4729,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>164</v>
       </c>
@@ -4743,7 +4744,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>148</v>
       </c>
@@ -4761,7 +4762,7 @@
         <v>+58 412-5885303</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>98</v>
       </c>
@@ -4776,7 +4777,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>260</v>
       </c>
@@ -4791,7 +4792,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>79</v>
       </c>
@@ -4806,7 +4807,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>60</v>
       </c>
@@ -4824,7 +4825,7 @@
         <v>+52 414-7234994</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>158</v>
       </c>
@@ -4842,7 +4843,7 @@
         <v>+1 (849) 763-2529</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>197</v>
       </c>
@@ -4851,7 +4852,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -4866,7 +4867,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>36</v>
       </c>
@@ -4875,7 +4876,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>123</v>
       </c>
@@ -4890,7 +4891,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>73</v>
       </c>
@@ -4905,7 +4906,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>85</v>
       </c>
@@ -4920,7 +4921,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>226</v>
       </c>
@@ -4935,7 +4936,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>143</v>
       </c>
@@ -4950,7 +4951,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>220</v>
       </c>
@@ -4959,7 +4960,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>256</v>
       </c>
@@ -4977,7 +4978,7 @@
         <v>+51 923 404 224</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>81</v>
       </c>
@@ -4992,7 +4993,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>19</v>
       </c>
@@ -5010,7 +5011,7 @@
         <v>+51 987 200 136</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>13</v>
       </c>
@@ -5028,7 +5029,7 @@
         <v>+51 972691544</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>187</v>
       </c>
@@ -5037,7 +5038,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>205</v>
       </c>
@@ -5046,7 +5047,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>213</v>
       </c>
@@ -5055,7 +5056,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>131</v>
       </c>
@@ -5070,7 +5071,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>232</v>
       </c>
@@ -5085,7 +5086,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>76</v>
       </c>
@@ -5100,7 +5101,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>49</v>
       </c>
@@ -5115,7 +5116,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>24</v>
       </c>
@@ -5124,7 +5125,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>102</v>
       </c>
@@ -5142,7 +5143,7 @@
         <v>+51 955 963 610</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>171</v>
       </c>
@@ -5157,7 +5158,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>182</v>
       </c>
@@ -5172,7 +5173,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>82</v>
       </c>
@@ -5187,7 +5188,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1</v>
       </c>
@@ -5205,7 +5206,7 @@
         <v>+51 945 323 097</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>209</v>
       </c>
@@ -5214,7 +5215,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>63</v>
       </c>
@@ -5232,7 +5233,7 @@
         <v>+51 965 373 102</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>228</v>
       </c>
@@ -5241,7 +5242,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>239</v>
       </c>
@@ -5250,7 +5251,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>216</v>
       </c>
@@ -5265,7 +5266,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="258" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>70</v>
       </c>
@@ -5283,7 +5284,7 @@
         <v>+51 955 834 817</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>144</v>
       </c>
@@ -5292,7 +5293,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>95</v>
       </c>
@@ -5301,7 +5302,7 @@
         <v xml:space="preserve">+ </v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
@@ -5319,7 +5320,7 @@
         <v>+54 9 3794 12-0368</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>11</v>
       </c>
@@ -5337,14 +5338,23 @@
         <v>+502 4760 5947</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
     </row>
-    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
@@ -5352,7 +5362,13 @@
       <c r="F273" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
+  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Bloody Cheese"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A262">
     <sortCondition ref="A2:A262"/>
   </sortState>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4B4782-80D2-41C9-A814-EBBB82C65607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF9D04E-FBD0-49E0-84A4-67E0A8F1F857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF9D04E-FBD0-49E0-84A4-67E0A8F1F857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2165274-01FF-4950-B407-E7C6452FB6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="383">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1183,6 +1183,9 @@
   </si>
   <si>
     <t>Honduras</t>
+  </si>
+  <si>
+    <t>991 176 689</t>
   </si>
 </sst>
 </file>
@@ -2143,10 +2146,13 @@
         <v>+55 71 9370-7438</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>255</v>
       </c>
+      <c r="B37" s="3" t="s">
+        <v>382</v>
+      </c>
       <c r="C37" t="s">
         <v>271</v>
       </c>
@@ -2155,7 +2161,7 @@
       </c>
       <c r="E37" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+51 </v>
+        <v>+51 991 176 689</v>
       </c>
     </row>
     <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -5366,6 +5372,7 @@
     <filterColumn colId="0">
       <filters>
         <filter val="Bloody Cheese"/>
+        <filter val="Chechin"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2165274-01FF-4950-B407-E7C6452FB6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7343C7D-9328-4764-BF89-51054314DA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="384">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1186,6 +1186,9 @@
   </si>
   <si>
     <t>991 176 689</t>
+  </si>
+  <si>
+    <t>424-2233503</t>
   </si>
 </sst>
 </file>
@@ -2041,7 +2044,7 @@
         <v>+58 412-7060529</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -2146,7 +2149,7 @@
         <v>+55 71 9370-7438</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>255</v>
       </c>
@@ -4264,10 +4267,13 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>198</v>
       </c>
+      <c r="B186" t="s">
+        <v>383</v>
+      </c>
       <c r="C186" t="s">
         <v>270</v>
       </c>
@@ -4276,7 +4282,7 @@
       </c>
       <c r="E186" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+58 </v>
+        <v>+58 424-2233503</v>
       </c>
     </row>
     <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -5371,8 +5377,7 @@
   <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Bloody Cheese"/>
-        <filter val="Chechin"/>
+        <filter val="Oscopio"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7343C7D-9328-4764-BF89-51054314DA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9E1023-A718-4CAB-ABD2-CBBD41E629DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="408">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1137,9 +1137,6 @@
     <t>414-7234994</t>
   </si>
   <si>
-    <t>1 (849)</t>
-  </si>
-  <si>
     <t>987 200 136</t>
   </si>
   <si>
@@ -1189,6 +1186,81 @@
   </si>
   <si>
     <t>424-2233503</t>
+  </si>
+  <si>
+    <t>1 771 306 4084</t>
+  </si>
+  <si>
+    <t>7868 0662</t>
+  </si>
+  <si>
+    <t>El Salvador</t>
+  </si>
+  <si>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>1 55 3845 6274</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6898-7574</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (787) 513-4231</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 412-1885430</t>
+  </si>
+  <si>
+    <t>1 56 3172 0225</t>
+  </si>
+  <si>
+    <t>414-8694655</t>
+  </si>
+  <si>
+    <t>5 1795768</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 479 233 6442</t>
+  </si>
+  <si>
+    <t>963 347 387</t>
+  </si>
+  <si>
+    <t>1 614 529 6392</t>
+  </si>
+  <si>
+    <t>1 287 154 7879</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 960 274 071</t>
+  </si>
+  <si>
+    <t>961 492 733</t>
+  </si>
+  <si>
+    <t>956 677 392</t>
+  </si>
+  <si>
+    <t>1 916 116 9432</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 771 112 3061</t>
+  </si>
+  <si>
+    <t>1 861 128 3193</t>
+  </si>
+  <si>
+    <t>937 332 268</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5 2756474</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 981 217 7384</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5 6467775</t>
   </si>
 </sst>
 </file>
@@ -1569,11 +1641,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1594,7 +1666,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1609,7 +1681,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>237</v>
       </c>
@@ -1627,7 +1699,7 @@
         <v>+51 933 668 277</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1645,7 +1717,7 @@
         <v>+51 980 596 555</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1663,7 +1735,7 @@
         <v>+58 424-7086947</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -1678,7 +1750,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>236</v>
       </c>
@@ -1696,22 +1768,25 @@
         <v>+58 412-1322018</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>194</v>
       </c>
       <c r="B8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C8" t="s">
         <v>272</v>
       </c>
+      <c r="D8">
+        <v>56</v>
+      </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
-        <v>+ 9 7927 3083</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+56 9 7927 3083</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -1726,7 +1801,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1744,7 +1819,7 @@
         <v>+51 985 699 608</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1762,7 +1837,7 @@
         <v>+52 1 56 1007 9583</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>192</v>
       </c>
@@ -1780,7 +1855,7 @@
         <v>+52 1 81 2944 2313</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1795,7 +1870,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1810,7 +1885,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>160</v>
       </c>
@@ -1825,7 +1900,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1843,19 +1918,22 @@
         <v>+51  984 190 584</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>149</v>
       </c>
       <c r="C17" t="s">
         <v>294</v>
       </c>
+      <c r="D17">
+        <v>57</v>
+      </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+57 </v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1873,7 +1951,7 @@
         <v>+51 984 267 160</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1891,19 +1969,22 @@
         <v>+51  912 858 811</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
       <c r="C20" t="s">
         <v>271</v>
       </c>
+      <c r="D20">
+        <v>51</v>
+      </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+51 </v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>136</v>
       </c>
@@ -1921,7 +2002,7 @@
         <v>+51 949 647 819</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1939,21 +2020,27 @@
         <v>+34  646 20 50 99</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>229</v>
       </c>
+      <c r="C23" t="s">
+        <v>271</v>
+      </c>
+      <c r="D23">
+        <v>51</v>
+      </c>
       <c r="E23" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+51 </v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>137</v>
       </c>
       <c r="B24" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C24" t="s">
         <v>268</v>
@@ -1966,7 +2053,7 @@
         <v>+52  1 222 102 8165</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1984,16 +2071,25 @@
         <v>+58 416-4398466</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>129</v>
       </c>
+      <c r="B26">
+        <v>91139028131</v>
+      </c>
+      <c r="C26" t="s">
+        <v>273</v>
+      </c>
+      <c r="D26">
+        <v>54</v>
+      </c>
       <c r="E26" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+54 91139028131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -2011,10 +2107,13 @@
         <v>+57 322 4761144</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
+      <c r="B28" t="s">
+        <v>383</v>
+      </c>
       <c r="C28" t="s">
         <v>268</v>
       </c>
@@ -2023,10 +2122,10 @@
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+52 </v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+52 1 771 306 4084</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>235</v>
       </c>
@@ -2044,7 +2143,7 @@
         <v>+58 412-7060529</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -2062,7 +2161,7 @@
         <v>+51 933448842</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -2077,16 +2176,25 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
+      <c r="B32">
+        <v>912358537</v>
+      </c>
+      <c r="C32" t="s">
+        <v>271</v>
+      </c>
+      <c r="D32">
+        <v>51</v>
+      </c>
       <c r="E32" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+51 912358537</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>180</v>
       </c>
@@ -2104,7 +2212,7 @@
         <v>+51 950 746 501</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -2122,16 +2230,22 @@
         <v>+54 9 3794 73 7373</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>119</v>
       </c>
+      <c r="C35" t="s">
+        <v>268</v>
+      </c>
+      <c r="D35">
+        <v>52</v>
+      </c>
       <c r="E35" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>181</v>
       </c>
@@ -2149,12 +2263,12 @@
         <v>+55 71 9370-7438</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>255</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C37" t="s">
         <v>271</v>
@@ -2167,7 +2281,7 @@
         <v>+51 991 176 689</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -2185,7 +2299,7 @@
         <v>+34 601 36 84 69</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2200,7 +2314,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>185</v>
       </c>
@@ -2218,7 +2332,7 @@
         <v>+51  917 057 695</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -2236,7 +2350,7 @@
         <v>+34 608 39 51 22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>222</v>
       </c>
@@ -2251,7 +2365,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>117</v>
       </c>
@@ -2266,7 +2380,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -2281,43 +2395,73 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>199</v>
       </c>
+      <c r="B45">
+        <v>93854880470</v>
+      </c>
+      <c r="C45" t="s">
+        <v>273</v>
+      </c>
+      <c r="D45">
+        <v>54</v>
+      </c>
       <c r="E45" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+54 93854880470</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>61</v>
       </c>
+      <c r="B46">
+        <v>51162846</v>
+      </c>
+      <c r="C46" t="s">
+        <v>266</v>
+      </c>
+      <c r="D46">
+        <v>53</v>
+      </c>
       <c r="E46" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+53 51162846</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>170</v>
       </c>
+      <c r="C47" t="s">
+        <v>279</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
       <c r="E47" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+1 </v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>57</v>
       </c>
+      <c r="C48" t="s">
+        <v>270</v>
+      </c>
+      <c r="D48">
+        <v>58</v>
+      </c>
       <c r="E48" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+58 </v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2335,7 +2479,7 @@
         <v>+51  920 449 371</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>68</v>
       </c>
@@ -2353,16 +2497,22 @@
         <v>+51  912 209 142</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
+      <c r="C51" t="s">
+        <v>271</v>
+      </c>
+      <c r="D51">
+        <v>51</v>
+      </c>
       <c r="E51" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+51 </v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -2380,7 +2530,7 @@
         <v>+505 8799 9543</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>125</v>
       </c>
@@ -2398,7 +2548,7 @@
         <v>+52 1 686 589 5829</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2416,7 +2566,7 @@
         <v>+51 992 067 030</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -2431,7 +2581,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -2446,16 +2596,22 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>231</v>
       </c>
+      <c r="C57" t="s">
+        <v>270</v>
+      </c>
+      <c r="D57">
+        <v>58</v>
+      </c>
       <c r="E57" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+58 </v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -2473,7 +2629,7 @@
         <v>+58  412-7396859</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -2491,7 +2647,7 @@
         <v>+52 1 921 208 0809</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>100</v>
       </c>
@@ -2506,15 +2662,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>166</v>
       </c>
       <c r="B61" t="s">
+        <v>379</v>
+      </c>
+      <c r="C61" t="s">
         <v>380</v>
-      </c>
-      <c r="C61" t="s">
-        <v>381</v>
       </c>
       <c r="D61">
         <v>504</v>
@@ -2524,16 +2680,25 @@
         <v>+504 3204-1711</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>128</v>
       </c>
+      <c r="B62">
+        <v>99797773</v>
+      </c>
+      <c r="C62" t="s">
+        <v>272</v>
+      </c>
+      <c r="D62">
+        <v>56</v>
+      </c>
       <c r="E62" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+56 99797773</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>223</v>
       </c>
@@ -2548,7 +2713,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -2566,43 +2731,73 @@
         <v>+1 305 8902347</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>168</v>
       </c>
+      <c r="B65" t="s">
+        <v>403</v>
+      </c>
+      <c r="C65" t="s">
+        <v>268</v>
+      </c>
+      <c r="D65">
+        <v>52</v>
+      </c>
       <c r="E65" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+52 1 861 128 3193</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>124</v>
       </c>
+      <c r="C66" t="s">
+        <v>270</v>
+      </c>
+      <c r="D66">
+        <v>58</v>
+      </c>
       <c r="E66" t="str">
         <f t="shared" ref="E66:E127" si="1">CONCATENATE("+",D66," ",B66)</f>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+58 </v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>177</v>
       </c>
+      <c r="C67" t="s">
+        <v>270</v>
+      </c>
+      <c r="D67">
+        <v>58</v>
+      </c>
       <c r="E67" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+58 </v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>217</v>
       </c>
+      <c r="B68">
+        <v>8341048014</v>
+      </c>
+      <c r="C68" t="s">
+        <v>268</v>
+      </c>
+      <c r="D68">
+        <v>52</v>
+      </c>
       <c r="E68" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+52 8341048014</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -2620,7 +2815,7 @@
         <v>+506  8936 2350</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>159</v>
       </c>
@@ -2638,7 +2833,7 @@
         <v>+1 (253) 212-8032</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -2653,34 +2848,52 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>195</v>
       </c>
+      <c r="C72" t="s">
+        <v>268</v>
+      </c>
+      <c r="D72">
+        <v>52</v>
+      </c>
       <c r="E72" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>110</v>
       </c>
+      <c r="C73" t="s">
+        <v>271</v>
+      </c>
+      <c r="D73">
+        <v>51</v>
+      </c>
       <c r="E73" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+51 </v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>188</v>
       </c>
+      <c r="C74" t="s">
+        <v>294</v>
+      </c>
+      <c r="D74">
+        <v>57</v>
+      </c>
       <c r="E74" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+57 </v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>241</v>
       </c>
@@ -2695,7 +2908,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>31</v>
       </c>
@@ -2713,7 +2926,7 @@
         <v>+51  912 058 374</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -2728,34 +2941,52 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>133</v>
       </c>
+      <c r="C78" t="s">
+        <v>270</v>
+      </c>
+      <c r="D78">
+        <v>58</v>
+      </c>
       <c r="E78" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+58 </v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
+      <c r="C79" t="s">
+        <v>271</v>
+      </c>
+      <c r="D79">
+        <v>51</v>
+      </c>
       <c r="E79" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+51 </v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>106</v>
       </c>
+      <c r="C80" t="s">
+        <v>268</v>
+      </c>
+      <c r="D80">
+        <v>52</v>
+      </c>
       <c r="E80" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>215</v>
       </c>
@@ -2773,25 +3004,37 @@
         <v>+593  96 083 0485</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>112</v>
       </c>
+      <c r="C82" t="s">
+        <v>306</v>
+      </c>
+      <c r="D82">
+        <v>505</v>
+      </c>
       <c r="E82" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+505 </v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
+      <c r="C83" t="s">
+        <v>268</v>
+      </c>
+      <c r="D83">
+        <v>52</v>
+      </c>
       <c r="E83" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -2809,16 +3052,22 @@
         <v>+51  983 379 394</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
+      <c r="C85" t="s">
+        <v>273</v>
+      </c>
+      <c r="D85">
+        <v>54</v>
+      </c>
       <c r="E85" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+54 </v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>162</v>
       </c>
@@ -2836,7 +3085,7 @@
         <v>+51 980 679 898</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>230</v>
       </c>
@@ -2851,25 +3100,43 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>139</v>
       </c>
+      <c r="B88" t="s">
+        <v>407</v>
+      </c>
+      <c r="C88" t="s">
+        <v>266</v>
+      </c>
+      <c r="D88">
+        <v>53</v>
+      </c>
       <c r="E88" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+53  5 6467775</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>176</v>
       </c>
+      <c r="B89">
+        <v>943126988</v>
+      </c>
+      <c r="C89" t="s">
+        <v>271</v>
+      </c>
+      <c r="D89">
+        <v>51</v>
+      </c>
       <c r="E89" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+51 943126988</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>122</v>
       </c>
@@ -2884,16 +3151,22 @@
         <v xml:space="preserve">+593 </v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>214</v>
       </c>
+      <c r="C91" t="s">
+        <v>268</v>
+      </c>
+      <c r="D91">
+        <v>52</v>
+      </c>
       <c r="E91" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>45</v>
       </c>
@@ -2911,7 +3184,7 @@
         <v>+54 9 3412 81-3587</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -2926,7 +3199,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>120</v>
       </c>
@@ -2944,7 +3217,7 @@
         <v>+57  302 5578252</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>206</v>
       </c>
@@ -2962,16 +3235,25 @@
         <v>+593 96 151 5565</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>244</v>
       </c>
+      <c r="B96" t="s">
+        <v>400</v>
+      </c>
+      <c r="C96" t="s">
+        <v>271</v>
+      </c>
+      <c r="D96">
+        <v>51</v>
+      </c>
       <c r="E96" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+51 956 677 392</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>240</v>
       </c>
@@ -2989,16 +3271,25 @@
         <v>+54 9 11 2783 9968</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>155</v>
       </c>
+      <c r="B98" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C98" t="s">
+        <v>271</v>
+      </c>
+      <c r="D98">
+        <v>51</v>
+      </c>
       <c r="E98" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+51 961 492 733</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>34</v>
       </c>
@@ -3016,7 +3307,7 @@
         <v>+53 5 1113536</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>140</v>
       </c>
@@ -3031,7 +3322,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>233</v>
       </c>
@@ -3046,7 +3337,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>141</v>
       </c>
@@ -3061,7 +3352,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>55</v>
       </c>
@@ -3079,7 +3370,7 @@
         <v>+1 (809) 658-5500</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>154</v>
       </c>
@@ -3097,7 +3388,7 @@
         <v>+58 424-1216695</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>169</v>
       </c>
@@ -3115,16 +3406,25 @@
         <v>+51 963 745 855</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>225</v>
       </c>
+      <c r="B106" t="s">
+        <v>398</v>
+      </c>
+      <c r="C106" t="s">
+        <v>271</v>
+      </c>
+      <c r="D106">
+        <v>51</v>
+      </c>
       <c r="E106" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+51  960 274 071</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -3134,30 +3434,48 @@
       <c r="C107" t="s">
         <v>316</v>
       </c>
+      <c r="D107">
+        <v>593</v>
+      </c>
       <c r="E107" t="str">
         <f t="shared" si="1"/>
-        <v>+ 98 768 2900</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+593 98 768 2900</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>94</v>
       </c>
+      <c r="C108" t="s">
+        <v>268</v>
+      </c>
+      <c r="D108">
+        <v>52</v>
+      </c>
       <c r="E108" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>247</v>
       </c>
+      <c r="B109" t="s">
+        <v>384</v>
+      </c>
+      <c r="C109" t="s">
+        <v>385</v>
+      </c>
+      <c r="D109">
+        <v>503</v>
+      </c>
       <c r="E109" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+503 7868 0662</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>243</v>
       </c>
@@ -3172,7 +3490,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>156</v>
       </c>
@@ -3190,16 +3508,25 @@
         <v>+58 414-4473628</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>43</v>
       </c>
+      <c r="B112">
+        <v>3054850698</v>
+      </c>
+      <c r="C112" t="s">
+        <v>294</v>
+      </c>
+      <c r="D112">
+        <v>57</v>
+      </c>
       <c r="E112" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+57 3054850698</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>224</v>
       </c>
@@ -3214,7 +3541,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>163</v>
       </c>
@@ -3229,25 +3556,40 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>56</v>
       </c>
+      <c r="C115" t="s">
+        <v>386</v>
+      </c>
+      <c r="D115">
+        <v>507</v>
+      </c>
       <c r="E115" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+507 </v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>150</v>
       </c>
+      <c r="B116" t="s">
+        <v>390</v>
+      </c>
+      <c r="C116" t="s">
+        <v>270</v>
+      </c>
+      <c r="D116">
+        <v>58</v>
+      </c>
       <c r="E116" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+58  412-1885430</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -3265,7 +3607,7 @@
         <v>+51  906 691 465</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3280,34 +3622,58 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>165</v>
       </c>
+      <c r="B119" t="s">
+        <v>389</v>
+      </c>
+      <c r="C119" t="s">
+        <v>279</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
+      </c>
       <c r="E119" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+1  (787) 513-4231</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>46</v>
       </c>
+      <c r="B120" t="s">
+        <v>388</v>
+      </c>
+      <c r="C120" t="s">
+        <v>386</v>
+      </c>
+      <c r="D120">
+        <v>507</v>
+      </c>
       <c r="E120" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+507  6898-7574</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>210</v>
       </c>
+      <c r="C121" t="s">
+        <v>268</v>
+      </c>
+      <c r="D121">
+        <v>52</v>
+      </c>
       <c r="E121" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3322,7 +3688,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>21</v>
       </c>
@@ -3340,7 +3706,7 @@
         <v>+51 996 668 615</v>
       </c>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>77</v>
       </c>
@@ -3355,25 +3721,40 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>250</v>
       </c>
+      <c r="B125" t="s">
+        <v>387</v>
+      </c>
+      <c r="C125" t="s">
+        <v>268</v>
+      </c>
+      <c r="D125">
+        <v>52</v>
+      </c>
       <c r="E125" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+52 1 55 3845 6274</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>193</v>
       </c>
+      <c r="C126" t="s">
+        <v>294</v>
+      </c>
+      <c r="D126">
+        <v>57</v>
+      </c>
       <c r="E126" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+57 </v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>254</v>
       </c>
@@ -3391,12 +3772,12 @@
         <v>+51  921 447 908</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>12</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C128" t="s">
         <v>271</v>
@@ -3409,7 +3790,7 @@
         <v>+51 976 413 331</v>
       </c>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>184</v>
       </c>
@@ -3424,16 +3805,22 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>101</v>
       </c>
+      <c r="C130" t="s">
+        <v>294</v>
+      </c>
+      <c r="D130">
+        <v>57</v>
+      </c>
       <c r="E130" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+57 </v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>157</v>
       </c>
@@ -3448,7 +3835,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>47</v>
       </c>
@@ -3463,16 +3850,25 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>221</v>
       </c>
+      <c r="B133" t="s">
+        <v>221</v>
+      </c>
+      <c r="C133" t="s">
+        <v>268</v>
+      </c>
+      <c r="D133">
+        <v>52</v>
+      </c>
       <c r="E133" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+52 Juni Frostheart</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>258</v>
       </c>
@@ -3490,16 +3886,25 @@
         <v>+54 9 11 2526 8333</v>
       </c>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>248</v>
       </c>
+      <c r="B135" t="s">
+        <v>395</v>
+      </c>
+      <c r="C135" t="s">
+        <v>271</v>
+      </c>
+      <c r="D135">
+        <v>51</v>
+      </c>
       <c r="E135" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+51 963 347 387</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -3517,16 +3922,22 @@
         <v>+52 1 81 2684 3183</v>
       </c>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>135</v>
       </c>
+      <c r="C137" t="s">
+        <v>268</v>
+      </c>
+      <c r="D137">
+        <v>52</v>
+      </c>
       <c r="E137" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>179</v>
       </c>
@@ -3541,7 +3952,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>109</v>
       </c>
@@ -3556,16 +3967,22 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
+      <c r="C140" t="s">
+        <v>268</v>
+      </c>
+      <c r="D140">
+        <v>52</v>
+      </c>
       <c r="E140" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>26</v>
       </c>
@@ -3583,7 +4000,7 @@
         <v>+57 302 3773516</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -3601,7 +4018,7 @@
         <v>+54  9 11 2372-2211</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>212</v>
       </c>
@@ -3619,7 +4036,7 @@
         <v>+51 960 749 072</v>
       </c>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -3637,7 +4054,7 @@
         <v>+51 984 784 816</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>245</v>
       </c>
@@ -3652,34 +4069,58 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>208</v>
       </c>
+      <c r="B146" t="s">
+        <v>396</v>
+      </c>
+      <c r="C146" t="s">
+        <v>268</v>
+      </c>
+      <c r="D146">
+        <v>52</v>
+      </c>
       <c r="E146" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+52 1 614 529 6392</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>211</v>
       </c>
+      <c r="B147" t="s">
+        <v>397</v>
+      </c>
+      <c r="C147" t="s">
+        <v>268</v>
+      </c>
+      <c r="D147">
+        <v>52</v>
+      </c>
       <c r="E147" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+52 1 287 154 7879</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>175</v>
       </c>
+      <c r="C148" t="s">
+        <v>268</v>
+      </c>
+      <c r="D148">
+        <v>52</v>
+      </c>
       <c r="E148" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>186</v>
       </c>
@@ -3694,7 +4135,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>65</v>
       </c>
@@ -3712,7 +4153,7 @@
         <v>+593 98 174 5020</v>
       </c>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -3727,7 +4168,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>118</v>
       </c>
@@ -3742,7 +4183,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>173</v>
       </c>
@@ -3760,7 +4201,7 @@
         <v>+52 1 771 297 6010</v>
       </c>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>178</v>
       </c>
@@ -3775,7 +4216,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>189</v>
       </c>
@@ -3793,7 +4234,7 @@
         <v>+52  1 983 752 2450</v>
       </c>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>93</v>
       </c>
@@ -3808,7 +4249,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>153</v>
       </c>
@@ -3826,7 +4267,7 @@
         <v>+58 424-6956750</v>
       </c>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>72</v>
       </c>
@@ -3844,7 +4285,7 @@
         <v>+51  965 337 810</v>
       </c>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>86</v>
       </c>
@@ -3859,7 +4300,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>87</v>
       </c>
@@ -3874,7 +4315,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>75</v>
       </c>
@@ -3889,7 +4330,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>201</v>
       </c>
@@ -3904,7 +4345,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>253</v>
       </c>
@@ -3922,12 +4363,12 @@
         <v>+51  945 349 568</v>
       </c>
     </row>
-    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>252</v>
       </c>
       <c r="B164" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C164" t="s">
         <v>268</v>
@@ -3940,7 +4381,7 @@
         <v>+52 1 735 162 2046</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>246</v>
       </c>
@@ -3958,7 +4399,7 @@
         <v>+51 970 857 085</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>78</v>
       </c>
@@ -3973,7 +4414,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>147</v>
       </c>
@@ -3991,12 +4432,12 @@
         <v>+52  1 673 472 3074</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>59</v>
       </c>
       <c r="B168" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C168" t="s">
         <v>273</v>
@@ -4009,7 +4450,7 @@
         <v>+54 9 2974 22-6785</v>
       </c>
     </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>242</v>
       </c>
@@ -4027,7 +4468,7 @@
         <v>+52 1 55 1805 8456</v>
       </c>
     </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>234</v>
       </c>
@@ -4042,7 +4483,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -4060,16 +4501,22 @@
         <v>+54  9 11 6135-9811</v>
       </c>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>202</v>
       </c>
+      <c r="C172" t="s">
+        <v>268</v>
+      </c>
+      <c r="D172">
+        <v>52</v>
+      </c>
       <c r="E172" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>219</v>
       </c>
@@ -4087,7 +4534,7 @@
         <v>+51 991 342 085</v>
       </c>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>69</v>
       </c>
@@ -4102,7 +4549,7 @@
         <v xml:space="preserve">+506 </v>
       </c>
     </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>218</v>
       </c>
@@ -4117,16 +4564,22 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>167</v>
       </c>
+      <c r="C176" t="s">
+        <v>271</v>
+      </c>
+      <c r="D176">
+        <v>51</v>
+      </c>
       <c r="E176" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+51 </v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>257</v>
       </c>
@@ -4144,25 +4597,37 @@
         <v>+53 5 6957902</v>
       </c>
     </row>
-    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>134</v>
       </c>
+      <c r="C178" t="s">
+        <v>268</v>
+      </c>
+      <c r="D178">
+        <v>52</v>
+      </c>
       <c r="E178" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>132</v>
       </c>
+      <c r="C179" t="s">
+        <v>268</v>
+      </c>
+      <c r="D179">
+        <v>52</v>
+      </c>
       <c r="E179" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>29</v>
       </c>
@@ -4180,7 +4645,7 @@
         <v>+51 977 404 957</v>
       </c>
     </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>53</v>
       </c>
@@ -4198,7 +4663,7 @@
         <v>+52 1 229 229 9515</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>64</v>
       </c>
@@ -4216,7 +4681,7 @@
         <v>+51 986 824 543</v>
       </c>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -4234,7 +4699,7 @@
         <v>+591 69865757</v>
       </c>
     </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>58</v>
       </c>
@@ -4252,7 +4717,7 @@
         <v>+506  7139 5493</v>
       </c>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>115</v>
       </c>
@@ -4272,7 +4737,7 @@
         <v>198</v>
       </c>
       <c r="B186" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C186" t="s">
         <v>270</v>
@@ -4285,16 +4750,25 @@
         <v>+58 424-2233503</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>207</v>
       </c>
+      <c r="B187">
+        <v>6644057270</v>
+      </c>
+      <c r="C187" t="s">
+        <v>268</v>
+      </c>
+      <c r="D187">
+        <v>52</v>
+      </c>
       <c r="E187" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+52 6644057270</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>3</v>
       </c>
@@ -4312,7 +4786,7 @@
         <v>+51 955 121 011</v>
       </c>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>172</v>
       </c>
@@ -4327,25 +4801,40 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>104</v>
       </c>
+      <c r="C190" t="s">
+        <v>268</v>
+      </c>
+      <c r="D190">
+        <v>52</v>
+      </c>
       <c r="E190" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>152</v>
       </c>
+      <c r="B191" t="s">
+        <v>394</v>
+      </c>
+      <c r="C191" t="s">
+        <v>268</v>
+      </c>
+      <c r="D191">
+        <v>52</v>
+      </c>
       <c r="E191" t="str">
         <f t="shared" ref="E191:E254" si="3">CONCATENATE("+",D191," ",B191)</f>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+52  1 479 233 6442</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>103</v>
       </c>
@@ -4360,16 +4849,22 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>259</v>
       </c>
+      <c r="C193" t="s">
+        <v>271</v>
+      </c>
+      <c r="D193">
+        <v>51</v>
+      </c>
       <c r="E193" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+51 </v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>80</v>
       </c>
@@ -4384,12 +4879,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>190</v>
       </c>
       <c r="B195" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C195" t="s">
         <v>268</v>
@@ -4402,16 +4897,22 @@
         <v>+52  1 756 103 6825</v>
       </c>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>204</v>
       </c>
+      <c r="C196" t="s">
+        <v>270</v>
+      </c>
+      <c r="D196">
+        <v>58</v>
+      </c>
       <c r="E196" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+58 </v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>174</v>
       </c>
@@ -4426,16 +4927,25 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>203</v>
       </c>
+      <c r="B198" t="s">
+        <v>406</v>
+      </c>
+      <c r="C198" t="s">
+        <v>268</v>
+      </c>
+      <c r="D198">
+        <v>52</v>
+      </c>
       <c r="E198" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+52  1 981 217 7384</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>48</v>
       </c>
@@ -4453,16 +4963,22 @@
         <v>+52 1 231 176 9718</v>
       </c>
     </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>249</v>
       </c>
+      <c r="C200" t="s">
+        <v>268</v>
+      </c>
+      <c r="D200">
+        <v>52</v>
+      </c>
       <c r="E200" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>200</v>
       </c>
@@ -4480,16 +4996,22 @@
         <v>+52  1 55 7364 9786</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>151</v>
       </c>
+      <c r="C202" t="s">
+        <v>272</v>
+      </c>
+      <c r="D202">
+        <v>56</v>
+      </c>
       <c r="E202" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+56 </v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>183</v>
       </c>
@@ -4504,34 +5026,58 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>196</v>
       </c>
+      <c r="B204" t="s">
+        <v>393</v>
+      </c>
+      <c r="C204" t="s">
+        <v>266</v>
+      </c>
+      <c r="D204">
+        <v>53</v>
+      </c>
       <c r="E204" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+53 5 1795768</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>96</v>
       </c>
+      <c r="C205" t="s">
+        <v>271</v>
+      </c>
+      <c r="D205">
+        <v>51</v>
+      </c>
       <c r="E205" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+51 </v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>251</v>
       </c>
+      <c r="B206" t="s">
+        <v>392</v>
+      </c>
+      <c r="C206" t="s">
+        <v>270</v>
+      </c>
+      <c r="D206">
+        <v>58</v>
+      </c>
       <c r="E206" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+58 414-8694655</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>97</v>
       </c>
@@ -4546,7 +5092,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>28</v>
       </c>
@@ -4564,7 +5110,7 @@
         <v>+51 981 000 049</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>191</v>
       </c>
@@ -4579,7 +5125,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>145</v>
       </c>
@@ -4597,7 +5143,7 @@
         <v>+56 9 7878 6558</v>
       </c>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>7</v>
       </c>
@@ -4615,7 +5161,7 @@
         <v>+51 973 614 848</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>15</v>
       </c>
@@ -4633,7 +5179,7 @@
         <v>+51 971 942 638</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>238</v>
       </c>
@@ -4648,7 +5194,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>40</v>
       </c>
@@ -4666,7 +5212,7 @@
         <v>+58 422-0376517</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>91</v>
       </c>
@@ -4681,7 +5227,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>227</v>
       </c>
@@ -4699,7 +5245,7 @@
         <v>+52  1 834 252 9665</v>
       </c>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>14</v>
       </c>
@@ -4717,16 +5263,22 @@
         <v>+506 6082 6653</v>
       </c>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>67</v>
       </c>
+      <c r="C218" t="s">
+        <v>266</v>
+      </c>
+      <c r="D218">
+        <v>503</v>
+      </c>
       <c r="E218" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+503 </v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>116</v>
       </c>
@@ -4741,7 +5293,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>164</v>
       </c>
@@ -4756,7 +5308,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>148</v>
       </c>
@@ -4774,7 +5326,7 @@
         <v>+58 412-5885303</v>
       </c>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>98</v>
       </c>
@@ -4789,7 +5341,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>260</v>
       </c>
@@ -4804,7 +5356,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>79</v>
       </c>
@@ -4819,7 +5371,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>60</v>
       </c>
@@ -4837,7 +5389,7 @@
         <v>+52 414-7234994</v>
       </c>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>158</v>
       </c>
@@ -4847,24 +5399,33 @@
       <c r="C226" t="s">
         <v>360</v>
       </c>
-      <c r="D226" t="s">
-        <v>366</v>
+      <c r="D226">
+        <v>1</v>
       </c>
       <c r="E226" t="str">
         <f t="shared" si="3"/>
-        <v>+1 (849) 763-2529</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+1 763-2529</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>197</v>
       </c>
+      <c r="B227" t="s">
+        <v>391</v>
+      </c>
+      <c r="C227" t="s">
+        <v>268</v>
+      </c>
+      <c r="D227">
+        <v>52</v>
+      </c>
       <c r="E227" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+52 1 56 3172 0225</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -4879,16 +5440,22 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>36</v>
       </c>
+      <c r="C229" t="s">
+        <v>271</v>
+      </c>
+      <c r="D229">
+        <v>51</v>
+      </c>
       <c r="E229" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+51 </v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>123</v>
       </c>
@@ -4903,7 +5470,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>73</v>
       </c>
@@ -4918,7 +5485,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>85</v>
       </c>
@@ -4933,7 +5500,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>226</v>
       </c>
@@ -4948,7 +5515,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>143</v>
       </c>
@@ -4963,21 +5530,27 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>220</v>
       </c>
+      <c r="C235" t="s">
+        <v>268</v>
+      </c>
+      <c r="D235">
+        <v>52</v>
+      </c>
       <c r="E235" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>256</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C236" t="s">
         <v>271</v>
@@ -4990,7 +5563,7 @@
         <v>+51 923 404 224</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>81</v>
       </c>
@@ -5005,12 +5578,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C238" t="s">
         <v>271</v>
@@ -5023,7 +5596,7 @@
         <v>+51 987 200 136</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>13</v>
       </c>
@@ -5041,34 +5614,55 @@
         <v>+51 972691544</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>187</v>
       </c>
+      <c r="B240" t="s">
+        <v>405</v>
+      </c>
+      <c r="C240" t="s">
+        <v>266</v>
+      </c>
+      <c r="D240">
+        <v>53</v>
+      </c>
       <c r="E240" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+53  5 2756474</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>205</v>
       </c>
+      <c r="C241" t="s">
+        <v>268</v>
+      </c>
+      <c r="D241">
+        <v>52</v>
+      </c>
       <c r="E241" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>213</v>
       </c>
+      <c r="C242" t="s">
+        <v>273</v>
+      </c>
+      <c r="D242">
+        <v>54</v>
+      </c>
       <c r="E242" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+54 </v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>131</v>
       </c>
@@ -5083,7 +5677,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>232</v>
       </c>
@@ -5098,7 +5692,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>76</v>
       </c>
@@ -5113,7 +5707,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>49</v>
       </c>
@@ -5128,21 +5722,30 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>24</v>
       </c>
+      <c r="B247" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C247" t="s">
+        <v>271</v>
+      </c>
+      <c r="D247">
+        <v>51</v>
+      </c>
       <c r="E247" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+51 937 332 268</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>102</v>
       </c>
       <c r="B248" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C248" t="s">
         <v>271</v>
@@ -5155,7 +5758,7 @@
         <v>+51 955 963 610</v>
       </c>
     </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>171</v>
       </c>
@@ -5170,7 +5773,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>182</v>
       </c>
@@ -5185,7 +5788,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>82</v>
       </c>
@@ -5200,12 +5803,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C252" t="s">
         <v>271</v>
@@ -5218,21 +5821,27 @@
         <v>+51 945 323 097</v>
       </c>
     </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>209</v>
       </c>
+      <c r="C253" t="s">
+        <v>268</v>
+      </c>
+      <c r="D253">
+        <v>52</v>
+      </c>
       <c r="E253" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>63</v>
       </c>
       <c r="B254" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C254" t="s">
         <v>271</v>
@@ -5245,25 +5854,43 @@
         <v>+51 965 373 102</v>
       </c>
     </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>228</v>
       </c>
+      <c r="B255" t="s">
+        <v>401</v>
+      </c>
+      <c r="C255" t="s">
+        <v>268</v>
+      </c>
+      <c r="D255">
+        <v>52</v>
+      </c>
       <c r="E255" t="str">
         <f t="shared" ref="E255:E262" si="4">CONCATENATE("+",D255," ",B255)</f>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+52 1 916 116 9432</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>239</v>
       </c>
+      <c r="B256" t="s">
+        <v>402</v>
+      </c>
+      <c r="C256" t="s">
+        <v>268</v>
+      </c>
+      <c r="D256">
+        <v>52</v>
+      </c>
       <c r="E256" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>+52  1 771 112 3061</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>216</v>
       </c>
@@ -5278,12 +5905,12 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="258" spans="1:6" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>70</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C258" t="s">
         <v>271</v>
@@ -5296,30 +5923,42 @@
         <v>+51 955 834 817</v>
       </c>
     </row>
-    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>144</v>
       </c>
+      <c r="C259" t="s">
+        <v>268</v>
+      </c>
+      <c r="D259">
+        <v>52</v>
+      </c>
       <c r="E259" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>95</v>
       </c>
+      <c r="C260" t="s">
+        <v>268</v>
+      </c>
+      <c r="D260">
+        <v>52</v>
+      </c>
       <c r="E260" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">+ </v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve">+52 </v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
       <c r="B261" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C261" t="s">
         <v>273</v>
@@ -5332,7 +5971,7 @@
         <v>+54 9 3794 12-0368</v>
       </c>
     </row>
-    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>11</v>
       </c>
@@ -5350,23 +5989,14 @@
         <v>+502 4760 5947</v>
       </c>
     </row>
-    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
     </row>
-    <row r="273" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
@@ -5374,13 +6004,7 @@
       <c r="F273" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Oscopio"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A262">
     <sortCondition ref="A2:A262"/>
   </sortState>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9E1023-A718-4CAB-ABD2-CBBD41E629DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2EEDCB-0CCC-4F05-846A-B32FDD94C679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="413">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1261,6 +1261,21 @@
   </si>
   <si>
     <t xml:space="preserve"> 5 6467775</t>
+  </si>
+  <si>
+    <t>1 444 674 9780</t>
+  </si>
+  <si>
+    <t>Kromsy Gg</t>
+  </si>
+  <si>
+    <t>333 2913156</t>
+  </si>
+  <si>
+    <t>Zelenic</t>
+  </si>
+  <si>
+    <t>9 11 2507-8576</t>
   </si>
 </sst>
 </file>
@@ -3662,6 +3677,9 @@
       <c r="A121" t="s">
         <v>210</v>
       </c>
+      <c r="B121" t="s">
+        <v>408</v>
+      </c>
       <c r="C121" t="s">
         <v>268</v>
       </c>
@@ -3670,7 +3688,7 @@
       </c>
       <c r="E121" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">+52 </v>
+        <v>+52 1 444 674 9780</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -5868,7 +5886,7 @@
         <v>52</v>
       </c>
       <c r="E255" t="str">
-        <f t="shared" ref="E255:E262" si="4">CONCATENATE("+",D255," ",B255)</f>
+        <f t="shared" ref="E255:E263" si="4">CONCATENATE("+",D255," ",B255)</f>
         <v>+52 1 916 116 9432</v>
       </c>
     </row>
@@ -5987,6 +6005,42 @@
       <c r="E262" t="str">
         <f t="shared" si="4"/>
         <v>+502 4760 5947</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>409</v>
+      </c>
+      <c r="B263" t="s">
+        <v>410</v>
+      </c>
+      <c r="C263" t="s">
+        <v>294</v>
+      </c>
+      <c r="D263">
+        <v>57</v>
+      </c>
+      <c r="E263" t="str">
+        <f t="shared" si="4"/>
+        <v>+57 333 2913156</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>411</v>
+      </c>
+      <c r="B264" t="s">
+        <v>412</v>
+      </c>
+      <c r="C264" t="s">
+        <v>273</v>
+      </c>
+      <c r="D264">
+        <v>54</v>
+      </c>
+      <c r="E264" t="str">
+        <f t="shared" ref="E264" si="5">CONCATENATE("+",D264," ",B264)</f>
+        <v>+54 9 11 2507-8576</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2EEDCB-0CCC-4F05-846A-B32FDD94C679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE7B649-1087-46F5-96AF-2DA685D51742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE7B649-1087-46F5-96AF-2DA685D51742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CB6909-50BC-4D97-B7A7-3943975A3C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -543,9 +543,6 @@
     <t>Naval 567</t>
   </si>
   <si>
-    <t>Dragonessi15</t>
-  </si>
-  <si>
     <t>HaoSigismondi</t>
   </si>
   <si>
@@ -1276,6 +1273,9 @@
   </si>
   <si>
     <t>9 11 2507-8576</t>
+  </si>
+  <si>
+    <t>Absol702</t>
   </si>
 </sst>
 </file>
@@ -1666,19 +1666,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B1" t="s">
         <v>261</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>262</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E1" t="s">
         <v>263</v>
-      </c>
-      <c r="D1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1686,7 +1686,7 @@
         <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D2">
         <v>51</v>
@@ -1698,13 +1698,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D3">
         <v>51</v>
@@ -1719,10 +1719,10 @@
         <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D4">
         <v>51</v>
@@ -1737,10 +1737,10 @@
         <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D5">
         <v>58</v>
@@ -1755,7 +1755,7 @@
         <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D6">
         <v>51</v>
@@ -1767,13 +1767,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D7">
         <v>58</v>
@@ -1785,13 +1785,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D8">
         <v>56</v>
@@ -1806,7 +1806,7 @@
         <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D9">
         <v>52</v>
@@ -1821,10 +1821,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D10">
         <v>51</v>
@@ -1839,10 +1839,10 @@
         <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D11">
         <v>52</v>
@@ -1854,13 +1854,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D12">
         <v>52</v>
@@ -1875,7 +1875,7 @@
         <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D13">
         <v>51</v>
@@ -1890,7 +1890,7 @@
         <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D14">
         <v>51</v>
@@ -1905,7 +1905,7 @@
         <v>160</v>
       </c>
       <c r="C15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D15">
         <v>51</v>
@@ -1920,10 +1920,10 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D16">
         <v>51</v>
@@ -1938,7 +1938,7 @@
         <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D17">
         <v>57</v>
@@ -1953,10 +1953,10 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C18" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D18">
         <v>51</v>
@@ -1971,10 +1971,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D19">
         <v>51</v>
@@ -1989,7 +1989,7 @@
         <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D20">
         <v>51</v>
@@ -2004,10 +2004,10 @@
         <v>136</v>
       </c>
       <c r="B21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D21">
         <v>51</v>
@@ -2022,10 +2022,10 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D22">
         <v>34</v>
@@ -2037,10 +2037,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D23">
         <v>51</v>
@@ -2055,10 +2055,10 @@
         <v>137</v>
       </c>
       <c r="B24" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C24" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D24">
         <v>52</v>
@@ -2073,10 +2073,10 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C25" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D25">
         <v>58</v>
@@ -2094,7 +2094,7 @@
         <v>91139028131</v>
       </c>
       <c r="C26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D26">
         <v>54</v>
@@ -2109,10 +2109,10 @@
         <v>138</v>
       </c>
       <c r="B27" t="s">
+        <v>292</v>
+      </c>
+      <c r="C27" t="s">
         <v>293</v>
-      </c>
-      <c r="C27" t="s">
-        <v>294</v>
       </c>
       <c r="D27">
         <v>57</v>
@@ -2127,10 +2127,10 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D28">
         <v>52</v>
@@ -2142,13 +2142,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B29" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D29">
         <v>58</v>
@@ -2166,7 +2166,7 @@
         <v>933448842</v>
       </c>
       <c r="C30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D30">
         <v>51</v>
@@ -2181,7 +2181,7 @@
         <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D31">
         <v>51</v>
@@ -2199,7 +2199,7 @@
         <v>912358537</v>
       </c>
       <c r="C32" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D32">
         <v>51</v>
@@ -2211,13 +2211,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C33" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D33">
         <v>51</v>
@@ -2232,10 +2232,10 @@
         <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C34" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D34">
         <v>54</v>
@@ -2250,7 +2250,7 @@
         <v>119</v>
       </c>
       <c r="C35" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D35">
         <v>52</v>
@@ -2262,13 +2262,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B36" t="s">
+        <v>296</v>
+      </c>
+      <c r="C36" t="s">
         <v>297</v>
-      </c>
-      <c r="C36" t="s">
-        <v>298</v>
       </c>
       <c r="D36">
         <v>55</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C37" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D37">
         <v>51</v>
@@ -2301,10 +2301,10 @@
         <v>121</v>
       </c>
       <c r="B38" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C38" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D38">
         <v>34</v>
@@ -2319,7 +2319,7 @@
         <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D39">
         <v>51</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D40">
         <v>51</v>
@@ -2352,10 +2352,10 @@
         <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C41" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D41">
         <v>34</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C42" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D42">
         <v>51</v>
@@ -2385,7 +2385,7 @@
         <v>117</v>
       </c>
       <c r="C43" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D43">
         <v>51</v>
@@ -2400,7 +2400,7 @@
         <v>99</v>
       </c>
       <c r="C44" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D44">
         <v>51</v>
@@ -2412,13 +2412,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B45">
         <v>93854880470</v>
       </c>
       <c r="C45" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D45">
         <v>54</v>
@@ -2436,7 +2436,7 @@
         <v>51162846</v>
       </c>
       <c r="C46" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D46">
         <v>53</v>
@@ -2448,10 +2448,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C47" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2466,7 +2466,7 @@
         <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D48">
         <v>58</v>
@@ -2481,10 +2481,10 @@
         <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C49" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D49">
         <v>51</v>
@@ -2499,10 +2499,10 @@
         <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C50" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D50">
         <v>51</v>
@@ -2517,7 +2517,7 @@
         <v>105</v>
       </c>
       <c r="C51" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D51">
         <v>51</v>
@@ -2532,10 +2532,10 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
+        <v>304</v>
+      </c>
+      <c r="C52" t="s">
         <v>305</v>
-      </c>
-      <c r="C52" t="s">
-        <v>306</v>
       </c>
       <c r="D52">
         <v>505</v>
@@ -2550,10 +2550,10 @@
         <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C53" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D53">
         <v>52</v>
@@ -2568,10 +2568,10 @@
         <v>161</v>
       </c>
       <c r="B54" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C54" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D54">
         <v>51</v>
@@ -2586,7 +2586,7 @@
         <v>108</v>
       </c>
       <c r="C55" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D55">
         <v>57</v>
@@ -2601,7 +2601,7 @@
         <v>9</v>
       </c>
       <c r="C56" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D56">
         <v>51</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C57" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D57">
         <v>58</v>
@@ -2631,10 +2631,10 @@
         <v>32</v>
       </c>
       <c r="B58" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C58" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D58">
         <v>58</v>
@@ -2649,10 +2649,10 @@
         <v>111</v>
       </c>
       <c r="B59" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C59" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D59">
         <v>52</v>
@@ -2667,7 +2667,7 @@
         <v>100</v>
       </c>
       <c r="C60" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D60">
         <v>51</v>
@@ -2682,10 +2682,10 @@
         <v>166</v>
       </c>
       <c r="B61" t="s">
+        <v>378</v>
+      </c>
+      <c r="C61" t="s">
         <v>379</v>
-      </c>
-      <c r="C61" t="s">
-        <v>380</v>
       </c>
       <c r="D61">
         <v>504</v>
@@ -2703,7 +2703,7 @@
         <v>99797773</v>
       </c>
       <c r="C62" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D62">
         <v>56</v>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C63" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D63">
         <v>51</v>
@@ -2733,10 +2733,10 @@
         <v>39</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2748,13 +2748,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>168</v>
+        <v>412</v>
       </c>
       <c r="B65" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C65" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D65">
         <v>52</v>
@@ -2769,7 +2769,7 @@
         <v>124</v>
       </c>
       <c r="C66" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D66">
         <v>58</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D67">
         <v>58</v>
@@ -2796,13 +2796,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B68">
         <v>8341048014</v>
       </c>
       <c r="C68" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D68">
         <v>52</v>
@@ -2817,10 +2817,10 @@
         <v>5</v>
       </c>
       <c r="B69" t="s">
+        <v>310</v>
+      </c>
+      <c r="C69" t="s">
         <v>311</v>
-      </c>
-      <c r="C69" t="s">
-        <v>312</v>
       </c>
       <c r="D69">
         <v>506</v>
@@ -2835,10 +2835,10 @@
         <v>159</v>
       </c>
       <c r="B70" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C70" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -2853,7 +2853,7 @@
         <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D71">
         <v>51</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C72" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D72">
         <v>52</v>
@@ -2883,7 +2883,7 @@
         <v>110</v>
       </c>
       <c r="C73" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D73">
         <v>51</v>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C74" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D74">
         <v>57</v>
@@ -2910,10 +2910,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C75" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D75">
         <v>54</v>
@@ -2928,10 +2928,10 @@
         <v>31</v>
       </c>
       <c r="B76" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C76" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D76">
         <v>51</v>
@@ -2946,7 +2946,7 @@
         <v>88</v>
       </c>
       <c r="C77" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D77">
         <v>51</v>
@@ -2961,7 +2961,7 @@
         <v>133</v>
       </c>
       <c r="C78" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D78">
         <v>58</v>
@@ -2976,7 +2976,7 @@
         <v>90</v>
       </c>
       <c r="C79" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D79">
         <v>51</v>
@@ -2991,7 +2991,7 @@
         <v>106</v>
       </c>
       <c r="C80" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D80">
         <v>52</v>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B81" t="s">
+        <v>314</v>
+      </c>
+      <c r="C81" t="s">
         <v>315</v>
-      </c>
-      <c r="C81" t="s">
-        <v>316</v>
       </c>
       <c r="D81">
         <v>593</v>
@@ -3024,7 +3024,7 @@
         <v>112</v>
       </c>
       <c r="C82" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D82">
         <v>505</v>
@@ -3039,7 +3039,7 @@
         <v>107</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D83">
         <v>52</v>
@@ -3054,10 +3054,10 @@
         <v>44</v>
       </c>
       <c r="B84" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C84" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D84">
         <v>51</v>
@@ -3072,7 +3072,7 @@
         <v>66</v>
       </c>
       <c r="C85" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D85">
         <v>54</v>
@@ -3087,10 +3087,10 @@
         <v>162</v>
       </c>
       <c r="B86" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C86" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D86">
         <v>51</v>
@@ -3102,10 +3102,10 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C87" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D87">
         <v>54</v>
@@ -3120,10 +3120,10 @@
         <v>139</v>
       </c>
       <c r="B88" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C88" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D88">
         <v>53</v>
@@ -3135,13 +3135,13 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B89">
         <v>943126988</v>
       </c>
       <c r="C89" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D89">
         <v>51</v>
@@ -3156,7 +3156,7 @@
         <v>122</v>
       </c>
       <c r="C90" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D90">
         <v>593</v>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C91" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D91">
         <v>52</v>
@@ -3186,10 +3186,10 @@
         <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C92" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D92">
         <v>54</v>
@@ -3204,7 +3204,7 @@
         <v>89</v>
       </c>
       <c r="C93" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D93">
         <v>51</v>
@@ -3219,10 +3219,10 @@
         <v>120</v>
       </c>
       <c r="B94" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C94" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D94">
         <v>57</v>
@@ -3234,13 +3234,13 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B95" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C95" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D95">
         <v>593</v>
@@ -3252,13 +3252,13 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B96" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C96" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D96">
         <v>51</v>
@@ -3270,13 +3270,13 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B97" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C97" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D97">
         <v>54</v>
@@ -3291,10 +3291,10 @@
         <v>155</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C98" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D98">
         <v>51</v>
@@ -3309,10 +3309,10 @@
         <v>34</v>
       </c>
       <c r="B99" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C99" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D99">
         <v>53</v>
@@ -3327,7 +3327,7 @@
         <v>140</v>
       </c>
       <c r="C100" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D100">
         <v>54</v>
@@ -3339,10 +3339,10 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C101" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D101">
         <v>54</v>
@@ -3357,7 +3357,7 @@
         <v>141</v>
       </c>
       <c r="C102" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D102">
         <v>57</v>
@@ -3372,10 +3372,10 @@
         <v>55</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C103" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3390,10 +3390,10 @@
         <v>154</v>
       </c>
       <c r="B104" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C104" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D104">
         <v>58</v>
@@ -3405,13 +3405,13 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B105" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C105" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D105">
         <v>51</v>
@@ -3423,13 +3423,13 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B106" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C106" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D106">
         <v>51</v>
@@ -3444,10 +3444,10 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C107" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D107">
         <v>593</v>
@@ -3462,7 +3462,7 @@
         <v>94</v>
       </c>
       <c r="C108" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D108">
         <v>52</v>
@@ -3474,13 +3474,13 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B109" t="s">
+        <v>383</v>
+      </c>
+      <c r="C109" t="s">
         <v>384</v>
-      </c>
-      <c r="C109" t="s">
-        <v>385</v>
       </c>
       <c r="D109">
         <v>503</v>
@@ -3492,10 +3492,10 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C110" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D110">
         <v>51</v>
@@ -3510,10 +3510,10 @@
         <v>156</v>
       </c>
       <c r="B111" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C111" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D111">
         <v>58</v>
@@ -3531,7 +3531,7 @@
         <v>3054850698</v>
       </c>
       <c r="C112" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D112">
         <v>57</v>
@@ -3543,10 +3543,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C113" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D113">
         <v>51</v>
@@ -3561,7 +3561,7 @@
         <v>163</v>
       </c>
       <c r="C114" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D114">
         <v>51</v>
@@ -3576,7 +3576,7 @@
         <v>56</v>
       </c>
       <c r="C115" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D115">
         <v>507</v>
@@ -3591,10 +3591,10 @@
         <v>150</v>
       </c>
       <c r="B116" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C116" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D116">
         <v>58</v>
@@ -3609,10 +3609,10 @@
         <v>130</v>
       </c>
       <c r="B117" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C117" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D117">
         <v>51</v>
@@ -3627,7 +3627,7 @@
         <v>146</v>
       </c>
       <c r="C118" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D118">
         <v>51</v>
@@ -3642,10 +3642,10 @@
         <v>165</v>
       </c>
       <c r="B119" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C119" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -3660,10 +3660,10 @@
         <v>46</v>
       </c>
       <c r="B120" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C120" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D120">
         <v>507</v>
@@ -3675,13 +3675,13 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B121" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C121" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D121">
         <v>52</v>
@@ -3696,7 +3696,7 @@
         <v>2</v>
       </c>
       <c r="C122" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D122">
         <v>51</v>
@@ -3711,10 +3711,10 @@
         <v>21</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C123" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D123">
         <v>51</v>
@@ -3729,7 +3729,7 @@
         <v>77</v>
       </c>
       <c r="C124" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D124">
         <v>51</v>
@@ -3741,13 +3741,13 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B125" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C125" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D125">
         <v>52</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C126" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D126">
         <v>57</v>
@@ -3774,13 +3774,13 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B127" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C127" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D127">
         <v>51</v>
@@ -3795,10 +3795,10 @@
         <v>12</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C128" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D128">
         <v>51</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C129" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D129">
         <v>51</v>
@@ -3828,7 +3828,7 @@
         <v>101</v>
       </c>
       <c r="C130" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D130">
         <v>57</v>
@@ -3843,7 +3843,7 @@
         <v>157</v>
       </c>
       <c r="C131" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D131">
         <v>54</v>
@@ -3858,7 +3858,7 @@
         <v>47</v>
       </c>
       <c r="C132" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D132">
         <v>57</v>
@@ -3870,13 +3870,13 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B133" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C133" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D133">
         <v>52</v>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B134" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C134" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D134">
         <v>54</v>
@@ -3906,13 +3906,13 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B135" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C135" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D135">
         <v>51</v>
@@ -3927,10 +3927,10 @@
         <v>33</v>
       </c>
       <c r="B136" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D136">
         <v>52</v>
@@ -3945,7 +3945,7 @@
         <v>135</v>
       </c>
       <c r="C137" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D137">
         <v>52</v>
@@ -3957,10 +3957,10 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C138" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D138">
         <v>51</v>
@@ -3975,7 +3975,7 @@
         <v>109</v>
       </c>
       <c r="C139" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D139">
         <v>51</v>
@@ -3990,7 +3990,7 @@
         <v>142</v>
       </c>
       <c r="C140" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D140">
         <v>52</v>
@@ -4005,10 +4005,10 @@
         <v>26</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C141" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D141">
         <v>57</v>
@@ -4023,10 +4023,10 @@
         <v>18</v>
       </c>
       <c r="B142" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C142" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D142">
         <v>54</v>
@@ -4038,13 +4038,13 @@
     </row>
     <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C143" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D143">
         <v>51</v>
@@ -4059,10 +4059,10 @@
         <v>25</v>
       </c>
       <c r="B144" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C144" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D144">
         <v>51</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C145" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D145">
         <v>51</v>
@@ -4089,13 +4089,13 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B146" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C146" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D146">
         <v>52</v>
@@ -4107,13 +4107,13 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B147" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C147" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D147">
         <v>52</v>
@@ -4125,10 +4125,10 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D148">
         <v>52</v>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C149" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D149">
         <v>54</v>
@@ -4158,10 +4158,10 @@
         <v>65</v>
       </c>
       <c r="B150" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C150" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D150" s="4">
         <v>593</v>
@@ -4176,7 +4176,7 @@
         <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D151">
         <v>51</v>
@@ -4191,7 +4191,7 @@
         <v>118</v>
       </c>
       <c r="C152" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D152">
         <v>51</v>
@@ -4203,13 +4203,13 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B153" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C153" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D153">
         <v>52</v>
@@ -4221,10 +4221,10 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D154">
         <v>51</v>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B155" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C155" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D155">
         <v>52</v>
@@ -4257,7 +4257,7 @@
         <v>93</v>
       </c>
       <c r="C156" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D156">
         <v>51</v>
@@ -4272,10 +4272,10 @@
         <v>153</v>
       </c>
       <c r="B157" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C157" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D157">
         <v>58</v>
@@ -4290,10 +4290,10 @@
         <v>72</v>
       </c>
       <c r="B158" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C158" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D158">
         <v>51</v>
@@ -4308,7 +4308,7 @@
         <v>86</v>
       </c>
       <c r="C159" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D159">
         <v>51</v>
@@ -4323,7 +4323,7 @@
         <v>87</v>
       </c>
       <c r="C160" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D160">
         <v>51</v>
@@ -4338,7 +4338,7 @@
         <v>75</v>
       </c>
       <c r="C161" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D161">
         <v>51</v>
@@ -4350,10 +4350,10 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C162" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D162">
         <v>54</v>
@@ -4365,13 +4365,13 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B163" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C163" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D163">
         <v>51</v>
@@ -4383,13 +4383,13 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B164" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C164" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D164">
         <v>52</v>
@@ -4401,13 +4401,13 @@
     </row>
     <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C165" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D165">
         <v>51</v>
@@ -4422,7 +4422,7 @@
         <v>78</v>
       </c>
       <c r="C166" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D166">
         <v>51</v>
@@ -4437,10 +4437,10 @@
         <v>147</v>
       </c>
       <c r="B167" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C167" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D167">
         <v>52</v>
@@ -4455,10 +4455,10 @@
         <v>59</v>
       </c>
       <c r="B168" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C168" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D168">
         <v>54</v>
@@ -4470,13 +4470,13 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B169" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C169" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D169">
         <v>52</v>
@@ -4488,10 +4488,10 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C170" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D170">
         <v>52</v>
@@ -4506,10 +4506,10 @@
         <v>35</v>
       </c>
       <c r="B171" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C171" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D171">
         <v>54</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C172" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D172">
         <v>52</v>
@@ -4536,13 +4536,13 @@
     </row>
     <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C173" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D173">
         <v>51</v>
@@ -4557,7 +4557,7 @@
         <v>69</v>
       </c>
       <c r="C174" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D174">
         <v>506</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C175" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D175">
         <v>51</v>
@@ -4587,7 +4587,7 @@
         <v>167</v>
       </c>
       <c r="C176" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D176">
         <v>51</v>
@@ -4599,13 +4599,13 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B177" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C177" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D177">
         <v>53</v>
@@ -4620,7 +4620,7 @@
         <v>134</v>
       </c>
       <c r="C178" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D178">
         <v>52</v>
@@ -4635,7 +4635,7 @@
         <v>132</v>
       </c>
       <c r="C179" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D179">
         <v>52</v>
@@ -4650,10 +4650,10 @@
         <v>29</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C180" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D180">
         <v>51</v>
@@ -4668,10 +4668,10 @@
         <v>53</v>
       </c>
       <c r="B181" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C181" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D181">
         <v>52</v>
@@ -4686,10 +4686,10 @@
         <v>64</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C182" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D182">
         <v>51</v>
@@ -4707,7 +4707,7 @@
         <v>69865757</v>
       </c>
       <c r="C183" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D183">
         <v>591</v>
@@ -4722,10 +4722,10 @@
         <v>58</v>
       </c>
       <c r="B184" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C184" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D184">
         <v>506</v>
@@ -4740,7 +4740,7 @@
         <v>115</v>
       </c>
       <c r="C185" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D185">
         <v>58</v>
@@ -4752,13 +4752,13 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B186" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C186" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D186">
         <v>58</v>
@@ -4770,13 +4770,13 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B187">
         <v>6644057270</v>
       </c>
       <c r="C187" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D187">
         <v>52</v>
@@ -4791,10 +4791,10 @@
         <v>3</v>
       </c>
       <c r="B188" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C188" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D188">
         <v>51</v>
@@ -4806,10 +4806,10 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C189" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D189">
         <v>51</v>
@@ -4824,7 +4824,7 @@
         <v>104</v>
       </c>
       <c r="C190" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D190">
         <v>52</v>
@@ -4839,10 +4839,10 @@
         <v>152</v>
       </c>
       <c r="B191" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C191" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D191">
         <v>52</v>
@@ -4857,7 +4857,7 @@
         <v>103</v>
       </c>
       <c r="C192" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D192">
         <v>51</v>
@@ -4869,10 +4869,10 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C193" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D193">
         <v>51</v>
@@ -4887,7 +4887,7 @@
         <v>80</v>
       </c>
       <c r="C194" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D194">
         <v>51</v>
@@ -4899,13 +4899,13 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B195" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C195" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D195">
         <v>52</v>
@@ -4917,10 +4917,10 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C196" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D196">
         <v>58</v>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C197" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D197">
         <v>51</v>
@@ -4947,13 +4947,13 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B198" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C198" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D198">
         <v>52</v>
@@ -4968,10 +4968,10 @@
         <v>48</v>
       </c>
       <c r="B199" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C199" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D199">
         <v>52</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C200" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D200">
         <v>52</v>
@@ -4998,13 +4998,13 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C201" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D201">
         <v>52</v>
@@ -5019,7 +5019,7 @@
         <v>151</v>
       </c>
       <c r="C202" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D202">
         <v>56</v>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C203" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D203">
         <v>51</v>
@@ -5046,13 +5046,13 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B204" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C204" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D204">
         <v>53</v>
@@ -5067,7 +5067,7 @@
         <v>96</v>
       </c>
       <c r="C205" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D205">
         <v>51</v>
@@ -5079,13 +5079,13 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B206" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C206" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D206">
         <v>58</v>
@@ -5100,7 +5100,7 @@
         <v>97</v>
       </c>
       <c r="C207" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D207">
         <v>51</v>
@@ -5115,10 +5115,10 @@
         <v>28</v>
       </c>
       <c r="B208" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C208" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D208">
         <v>51</v>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C209" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D209">
         <v>51</v>
@@ -5148,10 +5148,10 @@
         <v>145</v>
       </c>
       <c r="B210" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C210" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D210">
         <v>56</v>
@@ -5166,10 +5166,10 @@
         <v>7</v>
       </c>
       <c r="B211" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C211" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D211">
         <v>51</v>
@@ -5184,10 +5184,10 @@
         <v>15</v>
       </c>
       <c r="B212" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C212" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D212">
         <v>51</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C213" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D213">
         <v>51</v>
@@ -5217,10 +5217,10 @@
         <v>40</v>
       </c>
       <c r="B214" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C214" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D214">
         <v>58</v>
@@ -5235,7 +5235,7 @@
         <v>91</v>
       </c>
       <c r="C215" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D215">
         <v>51</v>
@@ -5247,13 +5247,13 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B216" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C216" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D216">
         <v>52</v>
@@ -5268,10 +5268,10 @@
         <v>14</v>
       </c>
       <c r="B217" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C217" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D217">
         <v>506</v>
@@ -5286,7 +5286,7 @@
         <v>67</v>
       </c>
       <c r="C218" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D218">
         <v>503</v>
@@ -5301,7 +5301,7 @@
         <v>116</v>
       </c>
       <c r="C219" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D219">
         <v>54</v>
@@ -5316,7 +5316,7 @@
         <v>164</v>
       </c>
       <c r="C220" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D220">
         <v>51</v>
@@ -5331,10 +5331,10 @@
         <v>148</v>
       </c>
       <c r="B221" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C221" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D221">
         <v>58</v>
@@ -5349,7 +5349,7 @@
         <v>98</v>
       </c>
       <c r="C222" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D222">
         <v>54</v>
@@ -5361,10 +5361,10 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D223">
         <v>51</v>
@@ -5379,7 +5379,7 @@
         <v>79</v>
       </c>
       <c r="C224" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D224">
         <v>51</v>
@@ -5394,10 +5394,10 @@
         <v>60</v>
       </c>
       <c r="B225" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C225" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D225">
         <v>52</v>
@@ -5412,10 +5412,10 @@
         <v>158</v>
       </c>
       <c r="B226" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C226" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D226">
         <v>1</v>
@@ -5427,13 +5427,13 @@
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B227" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C227" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D227">
         <v>52</v>
@@ -5448,7 +5448,7 @@
         <v>6</v>
       </c>
       <c r="C228" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D228">
         <v>51</v>
@@ -5463,7 +5463,7 @@
         <v>36</v>
       </c>
       <c r="C229" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D229">
         <v>51</v>
@@ -5478,7 +5478,7 @@
         <v>123</v>
       </c>
       <c r="C230" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D230">
         <v>54</v>
@@ -5493,7 +5493,7 @@
         <v>73</v>
       </c>
       <c r="C231" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D231">
         <v>51</v>
@@ -5508,7 +5508,7 @@
         <v>85</v>
       </c>
       <c r="C232" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D232">
         <v>51</v>
@@ -5520,10 +5520,10 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C233" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D233">
         <v>54</v>
@@ -5538,7 +5538,7 @@
         <v>143</v>
       </c>
       <c r="C234" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D234">
         <v>54</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C235" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D235">
         <v>52</v>
@@ -5565,13 +5565,13 @@
     </row>
     <row r="236" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C236" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D236">
         <v>51</v>
@@ -5586,7 +5586,7 @@
         <v>81</v>
       </c>
       <c r="C237" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D237">
         <v>51</v>
@@ -5601,10 +5601,10 @@
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C238" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D238">
         <v>51</v>
@@ -5622,7 +5622,7 @@
         <v>972691544</v>
       </c>
       <c r="C239" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D239">
         <v>51</v>
@@ -5634,13 +5634,13 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B240" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C240" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D240">
         <v>53</v>
@@ -5652,10 +5652,10 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C241" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D241">
         <v>52</v>
@@ -5667,10 +5667,10 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C242" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D242">
         <v>54</v>
@@ -5685,7 +5685,7 @@
         <v>131</v>
       </c>
       <c r="C243" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D243">
         <v>51</v>
@@ -5697,10 +5697,10 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C244" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D244">
         <v>54</v>
@@ -5715,7 +5715,7 @@
         <v>76</v>
       </c>
       <c r="C245" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D245">
         <v>51</v>
@@ -5730,7 +5730,7 @@
         <v>49</v>
       </c>
       <c r="C246" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D246">
         <v>51</v>
@@ -5745,10 +5745,10 @@
         <v>24</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C247" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D247">
         <v>51</v>
@@ -5763,10 +5763,10 @@
         <v>102</v>
       </c>
       <c r="B248" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C248" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D248">
         <v>51</v>
@@ -5778,10 +5778,10 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C249" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D249">
         <v>51</v>
@@ -5793,10 +5793,10 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C250" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D250">
         <v>51</v>
@@ -5811,7 +5811,7 @@
         <v>82</v>
       </c>
       <c r="C251" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D251">
         <v>51</v>
@@ -5826,10 +5826,10 @@
         <v>1</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C252" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D252">
         <v>51</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C253" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D253">
         <v>52</v>
@@ -5859,10 +5859,10 @@
         <v>63</v>
       </c>
       <c r="B254" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C254" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D254">
         <v>51</v>
@@ -5874,13 +5874,13 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B255" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C255" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D255">
         <v>52</v>
@@ -5892,13 +5892,13 @@
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B256" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C256" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D256">
         <v>52</v>
@@ -5910,10 +5910,10 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C257" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D257">
         <v>58</v>
@@ -5928,10 +5928,10 @@
         <v>70</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C258" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D258">
         <v>51</v>
@@ -5946,7 +5946,7 @@
         <v>144</v>
       </c>
       <c r="C259" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D259">
         <v>52</v>
@@ -5961,7 +5961,7 @@
         <v>95</v>
       </c>
       <c r="C260" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D260">
         <v>52</v>
@@ -5976,10 +5976,10 @@
         <v>62</v>
       </c>
       <c r="B261" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C261" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D261">
         <v>54</v>
@@ -5994,10 +5994,10 @@
         <v>11</v>
       </c>
       <c r="B262" t="s">
+        <v>360</v>
+      </c>
+      <c r="C262" t="s">
         <v>361</v>
-      </c>
-      <c r="C262" t="s">
-        <v>362</v>
       </c>
       <c r="D262">
         <v>502</v>
@@ -6009,13 +6009,13 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>408</v>
+      </c>
+      <c r="B263" t="s">
         <v>409</v>
       </c>
-      <c r="B263" t="s">
-        <v>410</v>
-      </c>
       <c r="C263" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D263">
         <v>57</v>
@@ -6027,13 +6027,13 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
+        <v>410</v>
+      </c>
+      <c r="B264" t="s">
         <v>411</v>
       </c>
-      <c r="B264" t="s">
-        <v>412</v>
-      </c>
       <c r="C264" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D264">
         <v>54</v>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CB6909-50BC-4D97-B7A7-3943975A3C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6881D2-0EB7-4EA3-A48C-7D427137626F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -5397,14 +5397,14 @@
         <v>364</v>
       </c>
       <c r="C225" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D225">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E225" t="str">
         <f t="shared" si="3"/>
-        <v>+52 414-7234994</v>
+        <v>+58 414-7234994</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6881D2-0EB7-4EA3-A48C-7D427137626F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9EF8CF-3640-43AC-9240-7047CE55E706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9EF8CF-3640-43AC-9240-7047CE55E706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FBFF19-96E9-4170-86C0-4B5099C8C685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="414">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1276,6 +1276,9 @@
   </si>
   <si>
     <t>Absol702</t>
+  </si>
+  <si>
+    <t>Peruano Tactico</t>
   </si>
 </sst>
 </file>
@@ -6039,8 +6042,23 @@
         <v>54</v>
       </c>
       <c r="E264" t="str">
-        <f t="shared" ref="E264" si="5">CONCATENATE("+",D264," ",B264)</f>
+        <f t="shared" ref="E264:E265" si="5">CONCATENATE("+",D264," ",B264)</f>
         <v>+54 9 11 2507-8576</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>413</v>
+      </c>
+      <c r="C265" t="s">
+        <v>270</v>
+      </c>
+      <c r="D265">
+        <v>51</v>
+      </c>
+      <c r="E265" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">+51 </v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FBFF19-96E9-4170-86C0-4B5099C8C685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F13734-799B-4C09-A5AF-3898221AE310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="416">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1279,6 +1279,12 @@
   </si>
   <si>
     <t>Peruano Tactico</t>
+  </si>
+  <si>
+    <t>mathixd1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 966 803 562</t>
   </si>
 </sst>
 </file>
@@ -3289,11 +3295,11 @@
         <v>+54 9 11 2783 9968</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>155</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" t="s">
         <v>398</v>
       </c>
       <c r="C98" t="s">
@@ -3370,11 +3376,11 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>55</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" t="s">
         <v>322</v>
       </c>
       <c r="C103" t="s">
@@ -5566,11 +5572,11 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>255</v>
       </c>
-      <c r="B236" s="3" t="s">
+      <c r="B236" t="s">
         <v>366</v>
       </c>
       <c r="C236" t="s">
@@ -5743,11 +5749,11 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="247" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>24</v>
       </c>
-      <c r="B247" s="3" t="s">
+      <c r="B247" t="s">
         <v>403</v>
       </c>
       <c r="C247" t="s">
@@ -5824,11 +5830,11 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="252" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1</v>
       </c>
-      <c r="B252" s="3" t="s">
+      <c r="B252" t="s">
         <v>368</v>
       </c>
       <c r="C252" t="s">
@@ -5926,11 +5932,11 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="258" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>70</v>
       </c>
-      <c r="B258" s="3" t="s">
+      <c r="B258" t="s">
         <v>370</v>
       </c>
       <c r="C258" t="s">
@@ -6059,6 +6065,24 @@
       <c r="E265" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">+51 </v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>414</v>
+      </c>
+      <c r="B266" t="s">
+        <v>415</v>
+      </c>
+      <c r="C266" t="s">
+        <v>270</v>
+      </c>
+      <c r="D266">
+        <v>51</v>
+      </c>
+      <c r="E266" t="str">
+        <f t="shared" ref="E266" si="6">CONCATENATE("+",D266," ",B266)</f>
+        <v>+51  966 803 562</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F13734-799B-4C09-A5AF-3898221AE310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1063A398-4AAD-42BA-B6F7-64608546BCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -975,9 +975,6 @@
     <t>Costa Rica</t>
   </si>
   <si>
-    <t>(253) 212-8032</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 912 058 374</t>
   </si>
   <si>
@@ -1005,9 +1002,6 @@
     <t>96 151 5565</t>
   </si>
   <si>
-    <t>(809) 658-5500</t>
-  </si>
-  <si>
     <t>424-1216695</t>
   </si>
   <si>
@@ -1125,9 +1119,6 @@
     <t>Guatemala</t>
   </si>
   <si>
-    <t>763-2529</t>
-  </si>
-  <si>
     <t>412-5885303</t>
   </si>
   <si>
@@ -1203,9 +1194,6 @@
     <t xml:space="preserve"> 6898-7574</t>
   </si>
   <si>
-    <t xml:space="preserve"> (787) 513-4231</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 412-1885430</t>
   </si>
   <si>
@@ -1285,6 +1273,18 @@
   </si>
   <si>
     <t xml:space="preserve"> 966 803 562</t>
+  </si>
+  <si>
+    <t>849 763-2529</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 787 513-4231</t>
+  </si>
+  <si>
+    <t>809 658-5500</t>
+  </si>
+  <si>
+    <t>253 212-8032</t>
   </si>
 </sst>
 </file>
@@ -1665,6 +1665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1690,7 +1691,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1705,7 +1706,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>236</v>
       </c>
@@ -1723,7 +1724,7 @@
         <v>+51 933 668 277</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1741,7 +1742,7 @@
         <v>+51 980 596 555</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1759,7 +1760,7 @@
         <v>+58 424-7086947</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -1774,7 +1775,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>235</v>
       </c>
@@ -1792,12 +1793,12 @@
         <v>+58 412-1322018</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>193</v>
       </c>
       <c r="B8" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C8" t="s">
         <v>271</v>
@@ -1810,7 +1811,7 @@
         <v>+56 9 7927 3083</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -1825,7 +1826,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1843,7 +1844,7 @@
         <v>+51 985 699 608</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1861,7 +1862,7 @@
         <v>+52 1 56 1007 9583</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>191</v>
       </c>
@@ -1879,7 +1880,7 @@
         <v>+52 1 81 2944 2313</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1894,7 +1895,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1909,7 +1910,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>160</v>
       </c>
@@ -1924,7 +1925,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1942,7 +1943,7 @@
         <v>+51  984 190 584</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>149</v>
       </c>
@@ -1957,7 +1958,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1975,7 +1976,7 @@
         <v>+51 984 267 160</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1993,7 +1994,7 @@
         <v>+51  912 858 811</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -2008,7 +2009,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>136</v>
       </c>
@@ -2026,7 +2027,7 @@
         <v>+51 949 647 819</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2044,7 +2045,7 @@
         <v>+34  646 20 50 99</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>228</v>
       </c>
@@ -2059,12 +2060,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>137</v>
       </c>
       <c r="B24" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C24" t="s">
         <v>267</v>
@@ -2077,7 +2078,7 @@
         <v>+52  1 222 102 8165</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -2095,7 +2096,7 @@
         <v>+58 416-4398466</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -2113,7 +2114,7 @@
         <v>+54 91139028131</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -2131,12 +2132,12 @@
         <v>+57 322 4761144</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C28" t="s">
         <v>267</v>
@@ -2149,7 +2150,7 @@
         <v>+52 1 771 306 4084</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>234</v>
       </c>
@@ -2167,7 +2168,7 @@
         <v>+58 412-7060529</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -2185,7 +2186,7 @@
         <v>+51 933448842</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -2200,7 +2201,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2218,7 +2219,7 @@
         <v>+51 912358537</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>179</v>
       </c>
@@ -2236,7 +2237,7 @@
         <v>+51 950 746 501</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -2254,7 +2255,7 @@
         <v>+54 9 3794 73 7373</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>119</v>
       </c>
@@ -2269,7 +2270,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>180</v>
       </c>
@@ -2287,12 +2288,12 @@
         <v>+55 71 9370-7438</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>254</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C37" t="s">
         <v>270</v>
@@ -2305,7 +2306,7 @@
         <v>+51 991 176 689</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -2323,7 +2324,7 @@
         <v>+34 601 36 84 69</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2338,7 +2339,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>184</v>
       </c>
@@ -2356,7 +2357,7 @@
         <v>+51  917 057 695</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -2374,7 +2375,7 @@
         <v>+34 608 39 51 22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>221</v>
       </c>
@@ -2389,7 +2390,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>117</v>
       </c>
@@ -2404,7 +2405,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -2419,7 +2420,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>198</v>
       </c>
@@ -2437,7 +2438,7 @@
         <v>+54 93854880470</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -2455,7 +2456,7 @@
         <v>+53 51162846</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>169</v>
       </c>
@@ -2470,7 +2471,7 @@
         <v xml:space="preserve">+1 </v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -2485,7 +2486,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2503,7 +2504,7 @@
         <v>+51  920 449 371</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>68</v>
       </c>
@@ -2521,7 +2522,7 @@
         <v>+51  912 209 142</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -2536,7 +2537,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -2554,7 +2555,7 @@
         <v>+505 8799 9543</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>125</v>
       </c>
@@ -2572,7 +2573,7 @@
         <v>+52 1 686 589 5829</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2590,7 +2591,7 @@
         <v>+51 992 067 030</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -2605,7 +2606,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -2620,7 +2621,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>230</v>
       </c>
@@ -2635,7 +2636,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -2653,7 +2654,7 @@
         <v>+58  412-7396859</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -2671,7 +2672,7 @@
         <v>+52 1 921 208 0809</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>100</v>
       </c>
@@ -2686,15 +2687,15 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>166</v>
       </c>
       <c r="B61" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C61" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D61">
         <v>504</v>
@@ -2704,7 +2705,7 @@
         <v>+504 3204-1711</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -2722,7 +2723,7 @@
         <v>+56 99797773</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>222</v>
       </c>
@@ -2737,7 +2738,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -2755,12 +2756,12 @@
         <v>+1 305 8902347</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B65" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C65" t="s">
         <v>267</v>
@@ -2773,7 +2774,7 @@
         <v>+52 1 861 128 3193</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>124</v>
       </c>
@@ -2788,7 +2789,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>176</v>
       </c>
@@ -2803,7 +2804,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>216</v>
       </c>
@@ -2821,7 +2822,7 @@
         <v>+52 8341048014</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -2844,7 +2845,7 @@
         <v>159</v>
       </c>
       <c r="B70" t="s">
-        <v>312</v>
+        <v>415</v>
       </c>
       <c r="C70" t="s">
         <v>278</v>
@@ -2854,10 +2855,10 @@
       </c>
       <c r="E70" t="str">
         <f t="shared" si="1"/>
-        <v>+1 (253) 212-8032</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>+1 253 212-8032</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -2872,7 +2873,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2887,7 +2888,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>110</v>
       </c>
@@ -2902,7 +2903,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>187</v>
       </c>
@@ -2917,7 +2918,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>240</v>
       </c>
@@ -2932,12 +2933,12 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>31</v>
       </c>
       <c r="B76" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C76" t="s">
         <v>270</v>
@@ -2950,7 +2951,7 @@
         <v>+51  912 058 374</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -2965,7 +2966,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>133</v>
       </c>
@@ -2980,7 +2981,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -2995,7 +2996,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>106</v>
       </c>
@@ -3010,15 +3011,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>214</v>
       </c>
       <c r="B81" t="s">
+        <v>313</v>
+      </c>
+      <c r="C81" t="s">
         <v>314</v>
-      </c>
-      <c r="C81" t="s">
-        <v>315</v>
       </c>
       <c r="D81">
         <v>593</v>
@@ -3028,7 +3029,7 @@
         <v>+593  96 083 0485</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -3043,7 +3044,7 @@
         <v xml:space="preserve">+505 </v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
@@ -3058,12 +3059,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>44</v>
       </c>
       <c r="B84" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C84" t="s">
         <v>270</v>
@@ -3076,7 +3077,7 @@
         <v>+51  983 379 394</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -3091,12 +3092,12 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>162</v>
       </c>
       <c r="B86" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C86" t="s">
         <v>270</v>
@@ -3109,7 +3110,7 @@
         <v>+51 980 679 898</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>229</v>
       </c>
@@ -3124,12 +3125,12 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>139</v>
       </c>
       <c r="B88" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C88" t="s">
         <v>265</v>
@@ -3142,7 +3143,7 @@
         <v>+53  5 6467775</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>175</v>
       </c>
@@ -3160,12 +3161,12 @@
         <v>+51 943126988</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>122</v>
       </c>
       <c r="C90" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D90">
         <v>593</v>
@@ -3175,7 +3176,7 @@
         <v xml:space="preserve">+593 </v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>213</v>
       </c>
@@ -3190,12 +3191,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C92" t="s">
         <v>272</v>
@@ -3208,7 +3209,7 @@
         <v>+54 9 3412 81-3587</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -3223,12 +3224,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>120</v>
       </c>
       <c r="B94" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C94" t="s">
         <v>293</v>
@@ -3241,15 +3242,15 @@
         <v>+57  302 5578252</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>205</v>
       </c>
       <c r="B95" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C95" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D95">
         <v>593</v>
@@ -3259,12 +3260,12 @@
         <v>+593 96 151 5565</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>243</v>
       </c>
       <c r="B96" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C96" t="s">
         <v>270</v>
@@ -3277,7 +3278,7 @@
         <v>+51 956 677 392</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>239</v>
       </c>
@@ -3295,12 +3296,12 @@
         <v>+54 9 11 2783 9968</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>155</v>
       </c>
       <c r="B98" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C98" t="s">
         <v>270</v>
@@ -3313,7 +3314,7 @@
         <v>+51 961 492 733</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>34</v>
       </c>
@@ -3331,7 +3332,7 @@
         <v>+53 5 1113536</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>140</v>
       </c>
@@ -3346,7 +3347,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>232</v>
       </c>
@@ -3361,7 +3362,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>141</v>
       </c>
@@ -3381,7 +3382,7 @@
         <v>55</v>
       </c>
       <c r="B103" t="s">
-        <v>322</v>
+        <v>414</v>
       </c>
       <c r="C103" t="s">
         <v>278</v>
@@ -3391,15 +3392,15 @@
       </c>
       <c r="E103" t="str">
         <f t="shared" si="1"/>
-        <v>+1 (809) 658-5500</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+        <v>+1 809 658-5500</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>154</v>
       </c>
       <c r="B104" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C104" t="s">
         <v>269</v>
@@ -3412,12 +3413,12 @@
         <v>+58 424-1216695</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>168</v>
       </c>
       <c r="B105" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C105" t="s">
         <v>270</v>
@@ -3430,12 +3431,12 @@
         <v>+51 963 745 855</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>224</v>
       </c>
       <c r="B106" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C106" t="s">
         <v>270</v>
@@ -3448,15 +3449,15 @@
         <v>+51  960 274 071</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C107" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D107">
         <v>593</v>
@@ -3466,7 +3467,7 @@
         <v>+593 98 768 2900</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -3481,15 +3482,15 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>246</v>
       </c>
       <c r="B109" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C109" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D109">
         <v>503</v>
@@ -3499,7 +3500,7 @@
         <v>+503 7868 0662</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>242</v>
       </c>
@@ -3514,12 +3515,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>156</v>
       </c>
       <c r="B111" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C111" t="s">
         <v>269</v>
@@ -3532,7 +3533,7 @@
         <v>+58 414-4473628</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>43</v>
       </c>
@@ -3550,7 +3551,7 @@
         <v>+57 3054850698</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>223</v>
       </c>
@@ -3565,7 +3566,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>163</v>
       </c>
@@ -3580,12 +3581,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>56</v>
       </c>
       <c r="C115" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D115">
         <v>507</v>
@@ -3595,12 +3596,12 @@
         <v xml:space="preserve">+507 </v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>150</v>
       </c>
       <c r="B116" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C116" t="s">
         <v>269</v>
@@ -3613,12 +3614,12 @@
         <v>+58  412-1885430</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
       <c r="B117" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C117" t="s">
         <v>270</v>
@@ -3631,7 +3632,7 @@
         <v>+51  906 691 465</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3651,7 +3652,7 @@
         <v>165</v>
       </c>
       <c r="B119" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="C119" t="s">
         <v>278</v>
@@ -3661,18 +3662,18 @@
       </c>
       <c r="E119" t="str">
         <f t="shared" si="1"/>
-        <v>+1  (787) 513-4231</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+        <v>+1  787 513-4231</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>46</v>
       </c>
       <c r="B120" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C120" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D120">
         <v>507</v>
@@ -3682,12 +3683,12 @@
         <v>+507  6898-7574</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>209</v>
       </c>
       <c r="B121" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C121" t="s">
         <v>267</v>
@@ -3700,7 +3701,7 @@
         <v>+52 1 444 674 9780</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3715,12 +3716,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>21</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C123" t="s">
         <v>270</v>
@@ -3733,7 +3734,7 @@
         <v>+51 996 668 615</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>77</v>
       </c>
@@ -3748,12 +3749,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>249</v>
       </c>
       <c r="B125" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C125" t="s">
         <v>267</v>
@@ -3766,7 +3767,7 @@
         <v>+52 1 55 3845 6274</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>192</v>
       </c>
@@ -3781,12 +3782,12 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>253</v>
       </c>
       <c r="B127" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C127" t="s">
         <v>270</v>
@@ -3799,12 +3800,12 @@
         <v>+51  921 447 908</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>12</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C128" t="s">
         <v>270</v>
@@ -3817,7 +3818,7 @@
         <v>+51 976 413 331</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>183</v>
       </c>
@@ -3832,7 +3833,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>101</v>
       </c>
@@ -3847,7 +3848,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>157</v>
       </c>
@@ -3862,7 +3863,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>47</v>
       </c>
@@ -3877,7 +3878,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>220</v>
       </c>
@@ -3895,7 +3896,7 @@
         <v>+52 Juni Frostheart</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>257</v>
       </c>
@@ -3913,12 +3914,12 @@
         <v>+54 9 11 2526 8333</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>247</v>
       </c>
       <c r="B135" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C135" t="s">
         <v>270</v>
@@ -3931,12 +3932,12 @@
         <v>+51 963 347 387</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>33</v>
       </c>
       <c r="B136" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C136" t="s">
         <v>267</v>
@@ -3949,7 +3950,7 @@
         <v>+52 1 81 2684 3183</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>135</v>
       </c>
@@ -3964,7 +3965,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>178</v>
       </c>
@@ -3979,7 +3980,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>109</v>
       </c>
@@ -3994,7 +3995,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -4009,12 +4010,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>26</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C141" t="s">
         <v>293</v>
@@ -4027,12 +4028,12 @@
         <v>+57 302 3773516</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>18</v>
       </c>
       <c r="B142" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C142" t="s">
         <v>272</v>
@@ -4045,12 +4046,12 @@
         <v>+54  9 11 2372-2211</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>211</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C143" t="s">
         <v>270</v>
@@ -4063,12 +4064,12 @@
         <v>+51 960 749 072</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>25</v>
       </c>
       <c r="B144" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C144" t="s">
         <v>270</v>
@@ -4081,7 +4082,7 @@
         <v>+51 984 784 816</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>244</v>
       </c>
@@ -4096,12 +4097,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>207</v>
       </c>
       <c r="B146" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C146" t="s">
         <v>267</v>
@@ -4114,12 +4115,12 @@
         <v>+52 1 614 529 6392</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>210</v>
       </c>
       <c r="B147" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C147" t="s">
         <v>267</v>
@@ -4132,7 +4133,7 @@
         <v>+52 1 287 154 7879</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>174</v>
       </c>
@@ -4147,7 +4148,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>185</v>
       </c>
@@ -4162,15 +4163,15 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>65</v>
       </c>
       <c r="B150" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C150" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D150" s="4">
         <v>593</v>
@@ -4180,7 +4181,7 @@
         <v>+593 98 174 5020</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -4195,7 +4196,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>118</v>
       </c>
@@ -4210,7 +4211,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>172</v>
       </c>
@@ -4228,7 +4229,7 @@
         <v>+52 1 771 297 6010</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>177</v>
       </c>
@@ -4243,12 +4244,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>188</v>
       </c>
       <c r="B155" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C155" t="s">
         <v>267</v>
@@ -4261,7 +4262,7 @@
         <v>+52  1 983 752 2450</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>93</v>
       </c>
@@ -4276,12 +4277,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>153</v>
       </c>
       <c r="B157" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C157" t="s">
         <v>269</v>
@@ -4294,12 +4295,12 @@
         <v>+58 424-6956750</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>72</v>
       </c>
       <c r="B158" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C158" t="s">
         <v>270</v>
@@ -4312,7 +4313,7 @@
         <v>+51  965 337 810</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>86</v>
       </c>
@@ -4327,7 +4328,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>87</v>
       </c>
@@ -4342,7 +4343,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>75</v>
       </c>
@@ -4357,7 +4358,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>200</v>
       </c>
@@ -4372,12 +4373,12 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>252</v>
       </c>
       <c r="B163" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C163" t="s">
         <v>270</v>
@@ -4390,12 +4391,12 @@
         <v>+51  945 349 568</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>251</v>
       </c>
       <c r="B164" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C164" t="s">
         <v>267</v>
@@ -4408,12 +4409,12 @@
         <v>+52 1 735 162 2046</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>245</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C165" t="s">
         <v>270</v>
@@ -4426,7 +4427,7 @@
         <v>+51 970 857 085</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>78</v>
       </c>
@@ -4441,12 +4442,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>147</v>
       </c>
       <c r="B167" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C167" t="s">
         <v>267</v>
@@ -4459,12 +4460,12 @@
         <v>+52  1 673 472 3074</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>59</v>
       </c>
       <c r="B168" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C168" t="s">
         <v>272</v>
@@ -4477,12 +4478,12 @@
         <v>+54 9 2974 22-6785</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>241</v>
       </c>
       <c r="B169" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C169" t="s">
         <v>267</v>
@@ -4495,7 +4496,7 @@
         <v>+52 1 55 1805 8456</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>233</v>
       </c>
@@ -4510,12 +4511,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>35</v>
       </c>
       <c r="B171" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C171" t="s">
         <v>272</v>
@@ -4528,7 +4529,7 @@
         <v>+54  9 11 6135-9811</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>201</v>
       </c>
@@ -4543,12 +4544,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>218</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C173" t="s">
         <v>270</v>
@@ -4561,7 +4562,7 @@
         <v>+51 991 342 085</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>69</v>
       </c>
@@ -4576,7 +4577,7 @@
         <v xml:space="preserve">+506 </v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>217</v>
       </c>
@@ -4591,7 +4592,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>167</v>
       </c>
@@ -4606,7 +4607,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>256</v>
       </c>
@@ -4624,7 +4625,7 @@
         <v>+53 5 6957902</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>134</v>
       </c>
@@ -4639,7 +4640,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>132</v>
       </c>
@@ -4654,12 +4655,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>29</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C180" t="s">
         <v>270</v>
@@ -4672,12 +4673,12 @@
         <v>+51 977 404 957</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>53</v>
       </c>
       <c r="B181" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C181" t="s">
         <v>267</v>
@@ -4690,12 +4691,12 @@
         <v>+52 1 229 229 9515</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>64</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C182" t="s">
         <v>270</v>
@@ -4708,7 +4709,7 @@
         <v>+51 986 824 543</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -4716,7 +4717,7 @@
         <v>69865757</v>
       </c>
       <c r="C183" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D183">
         <v>591</v>
@@ -4726,12 +4727,12 @@
         <v>+591 69865757</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>58</v>
       </c>
       <c r="B184" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C184" t="s">
         <v>311</v>
@@ -4744,7 +4745,7 @@
         <v>+506  7139 5493</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>115</v>
       </c>
@@ -4759,12 +4760,12 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>197</v>
       </c>
       <c r="B186" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C186" t="s">
         <v>269</v>
@@ -4777,7 +4778,7 @@
         <v>+58 424-2233503</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>206</v>
       </c>
@@ -4795,12 +4796,12 @@
         <v>+52 6644057270</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>3</v>
       </c>
       <c r="B188" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C188" t="s">
         <v>270</v>
@@ -4813,7 +4814,7 @@
         <v>+51 955 121 011</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>171</v>
       </c>
@@ -4828,7 +4829,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>104</v>
       </c>
@@ -4843,12 +4844,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>152</v>
       </c>
       <c r="B191" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C191" t="s">
         <v>267</v>
@@ -4861,7 +4862,7 @@
         <v>+52  1 479 233 6442</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>103</v>
       </c>
@@ -4876,7 +4877,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>258</v>
       </c>
@@ -4891,7 +4892,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>80</v>
       </c>
@@ -4906,12 +4907,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>189</v>
       </c>
       <c r="B195" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C195" t="s">
         <v>267</v>
@@ -4924,7 +4925,7 @@
         <v>+52  1 756 103 6825</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>203</v>
       </c>
@@ -4939,7 +4940,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>173</v>
       </c>
@@ -4954,12 +4955,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>202</v>
       </c>
       <c r="B198" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C198" t="s">
         <v>267</v>
@@ -4972,12 +4973,12 @@
         <v>+52  1 981 217 7384</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>48</v>
       </c>
       <c r="B199" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C199" t="s">
         <v>267</v>
@@ -4990,7 +4991,7 @@
         <v>+52 1 231 176 9718</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>248</v>
       </c>
@@ -5005,12 +5006,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C201" t="s">
         <v>267</v>
@@ -5023,7 +5024,7 @@
         <v>+52  1 55 7364 9786</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>151</v>
       </c>
@@ -5038,7 +5039,7 @@
         <v xml:space="preserve">+56 </v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>182</v>
       </c>
@@ -5053,12 +5054,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>195</v>
       </c>
       <c r="B204" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C204" t="s">
         <v>265</v>
@@ -5071,7 +5072,7 @@
         <v>+53 5 1795768</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>96</v>
       </c>
@@ -5086,12 +5087,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>250</v>
       </c>
       <c r="B206" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C206" t="s">
         <v>269</v>
@@ -5104,7 +5105,7 @@
         <v>+58 414-8694655</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>97</v>
       </c>
@@ -5119,12 +5120,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>28</v>
       </c>
       <c r="B208" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C208" t="s">
         <v>270</v>
@@ -5137,7 +5138,7 @@
         <v>+51 981 000 049</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>190</v>
       </c>
@@ -5152,12 +5153,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>145</v>
       </c>
       <c r="B210" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C210" t="s">
         <v>271</v>
@@ -5170,12 +5171,12 @@
         <v>+56 9 7878 6558</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>7</v>
       </c>
       <c r="B211" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C211" t="s">
         <v>270</v>
@@ -5188,12 +5189,12 @@
         <v>+51 973 614 848</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>15</v>
       </c>
       <c r="B212" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C212" t="s">
         <v>270</v>
@@ -5206,7 +5207,7 @@
         <v>+51 971 942 638</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>237</v>
       </c>
@@ -5221,12 +5222,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>40</v>
       </c>
       <c r="B214" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C214" t="s">
         <v>269</v>
@@ -5239,7 +5240,7 @@
         <v>+58 422-0376517</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>91</v>
       </c>
@@ -5254,12 +5255,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>226</v>
       </c>
       <c r="B216" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C216" t="s">
         <v>267</v>
@@ -5272,12 +5273,12 @@
         <v>+52  1 834 252 9665</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>14</v>
       </c>
       <c r="B217" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C217" t="s">
         <v>311</v>
@@ -5290,7 +5291,7 @@
         <v>+506 6082 6653</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>67</v>
       </c>
@@ -5305,7 +5306,7 @@
         <v xml:space="preserve">+503 </v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>116</v>
       </c>
@@ -5320,7 +5321,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>164</v>
       </c>
@@ -5335,12 +5336,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>148</v>
       </c>
       <c r="B221" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C221" t="s">
         <v>269</v>
@@ -5353,7 +5354,7 @@
         <v>+58 412-5885303</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>98</v>
       </c>
@@ -5368,7 +5369,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>259</v>
       </c>
@@ -5383,7 +5384,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>79</v>
       </c>
@@ -5398,12 +5399,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>60</v>
       </c>
       <c r="B225" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C225" t="s">
         <v>269</v>
@@ -5421,25 +5422,25 @@
         <v>158</v>
       </c>
       <c r="B226" t="s">
-        <v>362</v>
+        <v>412</v>
       </c>
       <c r="C226" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D226">
         <v>1</v>
       </c>
       <c r="E226" t="str">
         <f t="shared" si="3"/>
-        <v>+1 763-2529</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+        <v>+1 849 763-2529</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>196</v>
       </c>
       <c r="B227" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C227" t="s">
         <v>267</v>
@@ -5452,7 +5453,7 @@
         <v>+52 1 56 3172 0225</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -5467,7 +5468,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>36</v>
       </c>
@@ -5482,7 +5483,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>123</v>
       </c>
@@ -5497,7 +5498,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>73</v>
       </c>
@@ -5512,7 +5513,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>85</v>
       </c>
@@ -5527,7 +5528,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>225</v>
       </c>
@@ -5542,7 +5543,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>143</v>
       </c>
@@ -5557,7 +5558,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>219</v>
       </c>
@@ -5572,12 +5573,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>255</v>
       </c>
       <c r="B236" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C236" t="s">
         <v>270</v>
@@ -5590,7 +5591,7 @@
         <v>+51 923 404 224</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>81</v>
       </c>
@@ -5605,12 +5606,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>19</v>
       </c>
       <c r="B238" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C238" t="s">
         <v>270</v>
@@ -5623,7 +5624,7 @@
         <v>+51 987 200 136</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>13</v>
       </c>
@@ -5641,12 +5642,12 @@
         <v>+51 972691544</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>186</v>
       </c>
       <c r="B240" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C240" t="s">
         <v>265</v>
@@ -5659,7 +5660,7 @@
         <v>+53  5 2756474</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>204</v>
       </c>
@@ -5674,7 +5675,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>212</v>
       </c>
@@ -5689,7 +5690,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>131</v>
       </c>
@@ -5704,7 +5705,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>231</v>
       </c>
@@ -5719,7 +5720,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>76</v>
       </c>
@@ -5734,7 +5735,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>49</v>
       </c>
@@ -5749,12 +5750,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>24</v>
       </c>
       <c r="B247" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C247" t="s">
         <v>270</v>
@@ -5767,12 +5768,12 @@
         <v>+51 937 332 268</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>102</v>
       </c>
       <c r="B248" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C248" t="s">
         <v>270</v>
@@ -5785,7 +5786,7 @@
         <v>+51 955 963 610</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>170</v>
       </c>
@@ -5800,7 +5801,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>181</v>
       </c>
@@ -5815,7 +5816,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>82</v>
       </c>
@@ -5830,12 +5831,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1</v>
       </c>
       <c r="B252" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C252" t="s">
         <v>270</v>
@@ -5848,7 +5849,7 @@
         <v>+51 945 323 097</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>208</v>
       </c>
@@ -5863,12 +5864,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>63</v>
       </c>
       <c r="B254" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C254" t="s">
         <v>270</v>
@@ -5881,12 +5882,12 @@
         <v>+51 965 373 102</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>227</v>
       </c>
       <c r="B255" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C255" t="s">
         <v>267</v>
@@ -5899,12 +5900,12 @@
         <v>+52 1 916 116 9432</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>238</v>
       </c>
       <c r="B256" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C256" t="s">
         <v>267</v>
@@ -5917,7 +5918,7 @@
         <v>+52  1 771 112 3061</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>215</v>
       </c>
@@ -5932,12 +5933,12 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>70</v>
       </c>
       <c r="B258" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C258" t="s">
         <v>270</v>
@@ -5950,7 +5951,7 @@
         <v>+51 955 834 817</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>144</v>
       </c>
@@ -5965,7 +5966,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>95</v>
       </c>
@@ -5980,12 +5981,12 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
       <c r="B261" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C261" t="s">
         <v>272</v>
@@ -5998,15 +5999,15 @@
         <v>+54 9 3794 12-0368</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>11</v>
       </c>
       <c r="B262" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C262" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D262">
         <v>502</v>
@@ -6016,12 +6017,12 @@
         <v>+502 4760 5947</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B263" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C263" t="s">
         <v>293</v>
@@ -6034,12 +6035,12 @@
         <v>+57 333 2913156</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B264" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C264" t="s">
         <v>272</v>
@@ -6052,9 +6053,9 @@
         <v>+54 9 11 2507-8576</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C265" t="s">
         <v>270</v>
@@ -6067,12 +6068,12 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B266" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C266" t="s">
         <v>270</v>
@@ -6085,14 +6086,19 @@
         <v>+51  966 803 562</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
     </row>
-    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
@@ -6100,7 +6106,16 @@
       <c r="F273" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
+  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="(253) 212-8032"/>
+        <filter val="(787) 513-4231"/>
+        <filter val="(809) 658-5500"/>
+        <filter val="(849) 763-2529"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A262">
     <sortCondition ref="A2:A262"/>
   </sortState>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1063A398-4AAD-42BA-B6F7-64608546BCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F2BDC2-6944-47BD-A1BB-88C42A5BEE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="423">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1285,13 +1285,34 @@
   </si>
   <si>
     <t>253 212-8032</t>
+  </si>
+  <si>
+    <t>JohanSalapo</t>
+  </si>
+  <si>
+    <t>412-8286364</t>
+  </si>
+  <si>
+    <t>Jaspersd25</t>
+  </si>
+  <si>
+    <t>7279 9978</t>
+  </si>
+  <si>
+    <t>964 533 667</t>
+  </si>
+  <si>
+    <t>Fullhax</t>
+  </si>
+  <si>
+    <t>931 252 452</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1320,6 +1341,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1341,7 +1367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1351,6 +1377,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1665,7 +1692,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1691,7 +1717,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1706,7 +1732,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>236</v>
       </c>
@@ -1724,7 +1750,7 @@
         <v>+51 933 668 277</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1742,7 +1768,7 @@
         <v>+51 980 596 555</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1760,7 +1786,7 @@
         <v>+58 424-7086947</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -1775,7 +1801,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>235</v>
       </c>
@@ -1793,7 +1819,7 @@
         <v>+58 412-1322018</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>193</v>
       </c>
@@ -1811,7 +1837,7 @@
         <v>+56 9 7927 3083</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -1826,7 +1852,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1844,7 +1870,7 @@
         <v>+51 985 699 608</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1862,7 +1888,7 @@
         <v>+52 1 56 1007 9583</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>191</v>
       </c>
@@ -1880,7 +1906,7 @@
         <v>+52 1 81 2944 2313</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1895,7 +1921,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1910,7 +1936,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>160</v>
       </c>
@@ -1925,7 +1951,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1943,7 +1969,7 @@
         <v>+51  984 190 584</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>149</v>
       </c>
@@ -1958,7 +1984,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1976,7 +2002,7 @@
         <v>+51 984 267 160</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1994,7 +2020,7 @@
         <v>+51  912 858 811</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -2009,7 +2035,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>136</v>
       </c>
@@ -2027,7 +2053,7 @@
         <v>+51 949 647 819</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2045,7 +2071,7 @@
         <v>+34  646 20 50 99</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>228</v>
       </c>
@@ -2060,7 +2086,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>137</v>
       </c>
@@ -2078,7 +2104,7 @@
         <v>+52  1 222 102 8165</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -2096,7 +2122,7 @@
         <v>+58 416-4398466</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -2114,7 +2140,7 @@
         <v>+54 91139028131</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -2132,7 +2158,7 @@
         <v>+57 322 4761144</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -2150,7 +2176,7 @@
         <v>+52 1 771 306 4084</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>234</v>
       </c>
@@ -2168,7 +2194,7 @@
         <v>+58 412-7060529</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -2186,7 +2212,7 @@
         <v>+51 933448842</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -2201,7 +2227,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2219,7 +2245,7 @@
         <v>+51 912358537</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>179</v>
       </c>
@@ -2237,7 +2263,7 @@
         <v>+51 950 746 501</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -2255,7 +2281,7 @@
         <v>+54 9 3794 73 7373</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>119</v>
       </c>
@@ -2270,7 +2296,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>180</v>
       </c>
@@ -2288,7 +2314,7 @@
         <v>+55 71 9370-7438</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>254</v>
       </c>
@@ -2306,7 +2332,7 @@
         <v>+51 991 176 689</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -2324,7 +2350,7 @@
         <v>+34 601 36 84 69</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2339,7 +2365,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>184</v>
       </c>
@@ -2357,7 +2383,7 @@
         <v>+51  917 057 695</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -2375,7 +2401,7 @@
         <v>+34 608 39 51 22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>221</v>
       </c>
@@ -2390,7 +2416,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>117</v>
       </c>
@@ -2405,7 +2431,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -2420,7 +2446,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>198</v>
       </c>
@@ -2438,7 +2464,7 @@
         <v>+54 93854880470</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -2456,7 +2482,7 @@
         <v>+53 51162846</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>169</v>
       </c>
@@ -2471,7 +2497,7 @@
         <v xml:space="preserve">+1 </v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -2486,7 +2512,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2504,7 +2530,7 @@
         <v>+51  920 449 371</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>68</v>
       </c>
@@ -2522,7 +2548,7 @@
         <v>+51  912 209 142</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -2537,7 +2563,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -2555,7 +2581,7 @@
         <v>+505 8799 9543</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>125</v>
       </c>
@@ -2573,7 +2599,7 @@
         <v>+52 1 686 589 5829</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2591,7 +2617,7 @@
         <v>+51 992 067 030</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -2606,7 +2632,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -2621,7 +2647,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>230</v>
       </c>
@@ -2636,7 +2662,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -2654,7 +2680,7 @@
         <v>+58  412-7396859</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -2672,7 +2698,7 @@
         <v>+52 1 921 208 0809</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>100</v>
       </c>
@@ -2687,7 +2713,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>166</v>
       </c>
@@ -2705,7 +2731,7 @@
         <v>+504 3204-1711</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -2723,7 +2749,7 @@
         <v>+56 99797773</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>222</v>
       </c>
@@ -2738,7 +2764,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -2756,7 +2782,7 @@
         <v>+1 305 8902347</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>408</v>
       </c>
@@ -2774,7 +2800,7 @@
         <v>+52 1 861 128 3193</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>124</v>
       </c>
@@ -2789,7 +2815,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>176</v>
       </c>
@@ -2804,7 +2830,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>216</v>
       </c>
@@ -2822,7 +2848,7 @@
         <v>+52 8341048014</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -2858,7 +2884,7 @@
         <v>+1 253 212-8032</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -2873,7 +2899,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2888,7 +2914,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>110</v>
       </c>
@@ -2903,7 +2929,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>187</v>
       </c>
@@ -2918,7 +2944,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>240</v>
       </c>
@@ -2933,7 +2959,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>31</v>
       </c>
@@ -2951,7 +2977,7 @@
         <v>+51  912 058 374</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -2966,7 +2992,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>133</v>
       </c>
@@ -2981,7 +3007,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -2996,7 +3022,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>106</v>
       </c>
@@ -3011,7 +3037,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>214</v>
       </c>
@@ -3029,7 +3055,7 @@
         <v>+593  96 083 0485</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -3044,7 +3070,7 @@
         <v xml:space="preserve">+505 </v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
@@ -3059,7 +3085,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -3077,7 +3103,7 @@
         <v>+51  983 379 394</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -3092,7 +3118,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>162</v>
       </c>
@@ -3110,7 +3136,7 @@
         <v>+51 980 679 898</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>229</v>
       </c>
@@ -3125,7 +3151,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>139</v>
       </c>
@@ -3143,7 +3169,7 @@
         <v>+53  5 6467775</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>175</v>
       </c>
@@ -3161,7 +3187,7 @@
         <v>+51 943126988</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>122</v>
       </c>
@@ -3176,7 +3202,7 @@
         <v xml:space="preserve">+593 </v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>213</v>
       </c>
@@ -3191,7 +3217,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>45</v>
       </c>
@@ -3209,7 +3235,7 @@
         <v>+54 9 3412 81-3587</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -3224,7 +3250,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>120</v>
       </c>
@@ -3242,7 +3268,7 @@
         <v>+57  302 5578252</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>205</v>
       </c>
@@ -3260,7 +3286,7 @@
         <v>+593 96 151 5565</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>243</v>
       </c>
@@ -3278,7 +3304,7 @@
         <v>+51 956 677 392</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>239</v>
       </c>
@@ -3296,7 +3322,7 @@
         <v>+54 9 11 2783 9968</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>155</v>
       </c>
@@ -3314,7 +3340,7 @@
         <v>+51 961 492 733</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>34</v>
       </c>
@@ -3332,7 +3358,7 @@
         <v>+53 5 1113536</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>140</v>
       </c>
@@ -3347,7 +3373,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>232</v>
       </c>
@@ -3362,7 +3388,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>141</v>
       </c>
@@ -3395,7 +3421,7 @@
         <v>+1 809 658-5500</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>154</v>
       </c>
@@ -3413,7 +3439,7 @@
         <v>+58 424-1216695</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>168</v>
       </c>
@@ -3431,7 +3457,7 @@
         <v>+51 963 745 855</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>224</v>
       </c>
@@ -3449,7 +3475,7 @@
         <v>+51  960 274 071</v>
       </c>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -3467,7 +3493,7 @@
         <v>+593 98 768 2900</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -3482,7 +3508,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>246</v>
       </c>
@@ -3500,7 +3526,7 @@
         <v>+503 7868 0662</v>
       </c>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>242</v>
       </c>
@@ -3515,7 +3541,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>156</v>
       </c>
@@ -3533,7 +3559,7 @@
         <v>+58 414-4473628</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>43</v>
       </c>
@@ -3551,7 +3577,7 @@
         <v>+57 3054850698</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>223</v>
       </c>
@@ -3566,7 +3592,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>163</v>
       </c>
@@ -3581,7 +3607,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>56</v>
       </c>
@@ -3596,7 +3622,7 @@
         <v xml:space="preserve">+507 </v>
       </c>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>150</v>
       </c>
@@ -3614,7 +3640,7 @@
         <v>+58  412-1885430</v>
       </c>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -3632,7 +3658,7 @@
         <v>+51  906 691 465</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3665,7 +3691,7 @@
         <v>+1  787 513-4231</v>
       </c>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>46</v>
       </c>
@@ -3683,7 +3709,7 @@
         <v>+507  6898-7574</v>
       </c>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>209</v>
       </c>
@@ -3701,7 +3727,7 @@
         <v>+52 1 444 674 9780</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3716,7 +3742,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>21</v>
       </c>
@@ -3734,7 +3760,7 @@
         <v>+51 996 668 615</v>
       </c>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>77</v>
       </c>
@@ -3749,7 +3775,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>249</v>
       </c>
@@ -3767,7 +3793,7 @@
         <v>+52 1 55 3845 6274</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>192</v>
       </c>
@@ -3782,7 +3808,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>253</v>
       </c>
@@ -3800,7 +3826,7 @@
         <v>+51  921 447 908</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>12</v>
       </c>
@@ -3818,7 +3844,7 @@
         <v>+51 976 413 331</v>
       </c>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>183</v>
       </c>
@@ -3833,7 +3859,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>101</v>
       </c>
@@ -3848,7 +3874,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>157</v>
       </c>
@@ -3863,7 +3889,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>47</v>
       </c>
@@ -3878,7 +3904,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>220</v>
       </c>
@@ -3896,7 +3922,7 @@
         <v>+52 Juni Frostheart</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>257</v>
       </c>
@@ -3914,7 +3940,7 @@
         <v>+54 9 11 2526 8333</v>
       </c>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>247</v>
       </c>
@@ -3932,7 +3958,7 @@
         <v>+51 963 347 387</v>
       </c>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -3950,7 +3976,7 @@
         <v>+52 1 81 2684 3183</v>
       </c>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>135</v>
       </c>
@@ -3965,7 +3991,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>178</v>
       </c>
@@ -3980,7 +4006,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>109</v>
       </c>
@@ -3995,7 +4021,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -4010,7 +4036,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>26</v>
       </c>
@@ -4028,7 +4054,7 @@
         <v>+57 302 3773516</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -4046,7 +4072,7 @@
         <v>+54  9 11 2372-2211</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>211</v>
       </c>
@@ -4064,7 +4090,7 @@
         <v>+51 960 749 072</v>
       </c>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -4082,7 +4108,7 @@
         <v>+51 984 784 816</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>244</v>
       </c>
@@ -4097,7 +4123,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>207</v>
       </c>
@@ -4115,7 +4141,7 @@
         <v>+52 1 614 529 6392</v>
       </c>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>210</v>
       </c>
@@ -4133,7 +4159,7 @@
         <v>+52 1 287 154 7879</v>
       </c>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>174</v>
       </c>
@@ -4148,7 +4174,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>185</v>
       </c>
@@ -4163,7 +4189,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>65</v>
       </c>
@@ -4181,7 +4207,7 @@
         <v>+593 98 174 5020</v>
       </c>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -4196,7 +4222,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>118</v>
       </c>
@@ -4211,7 +4237,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>172</v>
       </c>
@@ -4229,7 +4255,7 @@
         <v>+52 1 771 297 6010</v>
       </c>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>177</v>
       </c>
@@ -4244,7 +4270,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>188</v>
       </c>
@@ -4262,7 +4288,7 @@
         <v>+52  1 983 752 2450</v>
       </c>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>93</v>
       </c>
@@ -4277,7 +4303,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>153</v>
       </c>
@@ -4295,7 +4321,7 @@
         <v>+58 424-6956750</v>
       </c>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>72</v>
       </c>
@@ -4313,7 +4339,7 @@
         <v>+51  965 337 810</v>
       </c>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>86</v>
       </c>
@@ -4328,7 +4354,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>87</v>
       </c>
@@ -4343,7 +4369,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>75</v>
       </c>
@@ -4358,7 +4384,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>200</v>
       </c>
@@ -4373,7 +4399,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>252</v>
       </c>
@@ -4391,7 +4417,7 @@
         <v>+51  945 349 568</v>
       </c>
     </row>
-    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>251</v>
       </c>
@@ -4409,7 +4435,7 @@
         <v>+52 1 735 162 2046</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>245</v>
       </c>
@@ -4427,7 +4453,7 @@
         <v>+51 970 857 085</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>78</v>
       </c>
@@ -4442,7 +4468,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>147</v>
       </c>
@@ -4460,7 +4486,7 @@
         <v>+52  1 673 472 3074</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>59</v>
       </c>
@@ -4478,7 +4504,7 @@
         <v>+54 9 2974 22-6785</v>
       </c>
     </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>241</v>
       </c>
@@ -4496,7 +4522,7 @@
         <v>+52 1 55 1805 8456</v>
       </c>
     </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>233</v>
       </c>
@@ -4511,7 +4537,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -4529,7 +4555,7 @@
         <v>+54  9 11 6135-9811</v>
       </c>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>201</v>
       </c>
@@ -4544,7 +4570,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>218</v>
       </c>
@@ -4562,7 +4588,7 @@
         <v>+51 991 342 085</v>
       </c>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>69</v>
       </c>
@@ -4577,7 +4603,7 @@
         <v xml:space="preserve">+506 </v>
       </c>
     </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>217</v>
       </c>
@@ -4592,7 +4618,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>167</v>
       </c>
@@ -4607,7 +4633,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>256</v>
       </c>
@@ -4625,7 +4651,7 @@
         <v>+53 5 6957902</v>
       </c>
     </row>
-    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>134</v>
       </c>
@@ -4640,7 +4666,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>132</v>
       </c>
@@ -4655,7 +4681,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>29</v>
       </c>
@@ -4673,7 +4699,7 @@
         <v>+51 977 404 957</v>
       </c>
     </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>53</v>
       </c>
@@ -4691,7 +4717,7 @@
         <v>+52 1 229 229 9515</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>64</v>
       </c>
@@ -4709,7 +4735,7 @@
         <v>+51 986 824 543</v>
       </c>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -4727,7 +4753,7 @@
         <v>+591 69865757</v>
       </c>
     </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>58</v>
       </c>
@@ -4745,7 +4771,7 @@
         <v>+506  7139 5493</v>
       </c>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>115</v>
       </c>
@@ -4760,7 +4786,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>197</v>
       </c>
@@ -4778,7 +4804,7 @@
         <v>+58 424-2233503</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>206</v>
       </c>
@@ -4796,7 +4822,7 @@
         <v>+52 6644057270</v>
       </c>
     </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>3</v>
       </c>
@@ -4814,7 +4840,7 @@
         <v>+51 955 121 011</v>
       </c>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>171</v>
       </c>
@@ -4829,7 +4855,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>104</v>
       </c>
@@ -4844,7 +4870,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>152</v>
       </c>
@@ -4862,7 +4888,7 @@
         <v>+52  1 479 233 6442</v>
       </c>
     </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>103</v>
       </c>
@@ -4877,7 +4903,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>258</v>
       </c>
@@ -4892,7 +4918,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>80</v>
       </c>
@@ -4907,7 +4933,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>189</v>
       </c>
@@ -4925,7 +4951,7 @@
         <v>+52  1 756 103 6825</v>
       </c>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>203</v>
       </c>
@@ -4940,7 +4966,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>173</v>
       </c>
@@ -4955,7 +4981,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>202</v>
       </c>
@@ -4973,7 +4999,7 @@
         <v>+52  1 981 217 7384</v>
       </c>
     </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>48</v>
       </c>
@@ -4991,7 +5017,7 @@
         <v>+52 1 231 176 9718</v>
       </c>
     </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>248</v>
       </c>
@@ -5006,7 +5032,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -5024,7 +5050,7 @@
         <v>+52  1 55 7364 9786</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>151</v>
       </c>
@@ -5039,7 +5065,7 @@
         <v xml:space="preserve">+56 </v>
       </c>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>182</v>
       </c>
@@ -5054,7 +5080,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>195</v>
       </c>
@@ -5072,7 +5098,7 @@
         <v>+53 5 1795768</v>
       </c>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>96</v>
       </c>
@@ -5087,7 +5113,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>250</v>
       </c>
@@ -5105,7 +5131,7 @@
         <v>+58 414-8694655</v>
       </c>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>97</v>
       </c>
@@ -5120,7 +5146,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>28</v>
       </c>
@@ -5138,7 +5164,7 @@
         <v>+51 981 000 049</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>190</v>
       </c>
@@ -5153,7 +5179,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>145</v>
       </c>
@@ -5171,7 +5197,7 @@
         <v>+56 9 7878 6558</v>
       </c>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>7</v>
       </c>
@@ -5189,7 +5215,7 @@
         <v>+51 973 614 848</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>15</v>
       </c>
@@ -5207,7 +5233,7 @@
         <v>+51 971 942 638</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>237</v>
       </c>
@@ -5222,7 +5248,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>40</v>
       </c>
@@ -5240,7 +5266,7 @@
         <v>+58 422-0376517</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>91</v>
       </c>
@@ -5255,7 +5281,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>226</v>
       </c>
@@ -5273,7 +5299,7 @@
         <v>+52  1 834 252 9665</v>
       </c>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>14</v>
       </c>
@@ -5291,7 +5317,7 @@
         <v>+506 6082 6653</v>
       </c>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>67</v>
       </c>
@@ -5306,7 +5332,7 @@
         <v xml:space="preserve">+503 </v>
       </c>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>116</v>
       </c>
@@ -5321,7 +5347,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>164</v>
       </c>
@@ -5336,7 +5362,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>148</v>
       </c>
@@ -5354,7 +5380,7 @@
         <v>+58 412-5885303</v>
       </c>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>98</v>
       </c>
@@ -5369,7 +5395,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>259</v>
       </c>
@@ -5384,7 +5410,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>79</v>
       </c>
@@ -5399,7 +5425,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>60</v>
       </c>
@@ -5435,7 +5461,7 @@
         <v>+1 849 763-2529</v>
       </c>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>196</v>
       </c>
@@ -5453,7 +5479,7 @@
         <v>+52 1 56 3172 0225</v>
       </c>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -5468,7 +5494,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>36</v>
       </c>
@@ -5483,7 +5509,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>123</v>
       </c>
@@ -5498,7 +5524,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>73</v>
       </c>
@@ -5513,7 +5539,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>85</v>
       </c>
@@ -5528,7 +5554,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>225</v>
       </c>
@@ -5543,7 +5569,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>143</v>
       </c>
@@ -5558,7 +5584,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>219</v>
       </c>
@@ -5573,7 +5599,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>255</v>
       </c>
@@ -5591,7 +5617,7 @@
         <v>+51 923 404 224</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>81</v>
       </c>
@@ -5606,7 +5632,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>19</v>
       </c>
@@ -5624,7 +5650,7 @@
         <v>+51 987 200 136</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>13</v>
       </c>
@@ -5642,7 +5668,7 @@
         <v>+51 972691544</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>186</v>
       </c>
@@ -5660,7 +5686,7 @@
         <v>+53  5 2756474</v>
       </c>
     </row>
-    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>204</v>
       </c>
@@ -5675,7 +5701,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>212</v>
       </c>
@@ -5690,7 +5716,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>131</v>
       </c>
@@ -5705,7 +5731,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>231</v>
       </c>
@@ -5720,7 +5746,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>76</v>
       </c>
@@ -5735,7 +5761,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>49</v>
       </c>
@@ -5750,7 +5776,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>24</v>
       </c>
@@ -5768,7 +5794,7 @@
         <v>+51 937 332 268</v>
       </c>
     </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>102</v>
       </c>
@@ -5786,10 +5812,13 @@
         <v>+51 955 963 610</v>
       </c>
     </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>170</v>
       </c>
+      <c r="B249" t="s">
+        <v>422</v>
+      </c>
       <c r="C249" t="s">
         <v>270</v>
       </c>
@@ -5798,10 +5827,10 @@
       </c>
       <c r="E249" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>+51 931 252 452</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>181</v>
       </c>
@@ -5816,7 +5845,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>82</v>
       </c>
@@ -5831,7 +5860,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1</v>
       </c>
@@ -5849,7 +5878,7 @@
         <v>+51 945 323 097</v>
       </c>
     </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>208</v>
       </c>
@@ -5864,7 +5893,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>63</v>
       </c>
@@ -5882,7 +5911,7 @@
         <v>+51 965 373 102</v>
       </c>
     </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>227</v>
       </c>
@@ -5900,7 +5929,7 @@
         <v>+52 1 916 116 9432</v>
       </c>
     </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>238</v>
       </c>
@@ -5918,7 +5947,7 @@
         <v>+52  1 771 112 3061</v>
       </c>
     </row>
-    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>215</v>
       </c>
@@ -5933,7 +5962,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>70</v>
       </c>
@@ -5951,7 +5980,7 @@
         <v>+51 955 834 817</v>
       </c>
     </row>
-    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>144</v>
       </c>
@@ -5966,7 +5995,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>95</v>
       </c>
@@ -5981,7 +6010,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
@@ -5999,7 +6028,7 @@
         <v>+54 9 3794 12-0368</v>
       </c>
     </row>
-    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>11</v>
       </c>
@@ -6017,7 +6046,7 @@
         <v>+502 4760 5947</v>
       </c>
     </row>
-    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>404</v>
       </c>
@@ -6035,7 +6064,7 @@
         <v>+57 333 2913156</v>
       </c>
     </row>
-    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>406</v>
       </c>
@@ -6053,7 +6082,7 @@
         <v>+54 9 11 2507-8576</v>
       </c>
     </row>
-    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>409</v>
       </c>
@@ -6068,7 +6097,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>410</v>
       </c>
@@ -6086,19 +6115,68 @@
         <v>+51  966 803 562</v>
       </c>
     </row>
-    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>416</v>
+      </c>
+      <c r="B267" t="s">
+        <v>417</v>
+      </c>
+      <c r="C267" t="s">
+        <v>269</v>
+      </c>
+      <c r="D267">
+        <v>58</v>
+      </c>
+      <c r="E267" t="str">
+        <f t="shared" ref="E267:E269" si="7">CONCATENATE("+",D267," ",B267)</f>
+        <v>+58 412-8286364</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>418</v>
+      </c>
+      <c r="B268" t="s">
+        <v>419</v>
+      </c>
+      <c r="C268" t="s">
+        <v>381</v>
+      </c>
+      <c r="D268">
+        <v>503</v>
+      </c>
+      <c r="E268" t="str">
+        <f t="shared" si="7"/>
+        <v>+503 7279 9978</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>421</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="C269" t="s">
+        <v>270</v>
+      </c>
+      <c r="D269">
+        <v>51</v>
+      </c>
+      <c r="E269" t="str">
+        <f t="shared" si="7"/>
+        <v>+51 964 533 667</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
     </row>
-    <row r="273" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
@@ -6106,16 +6184,7 @@
       <c r="F273" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="(253) 212-8032"/>
-        <filter val="(787) 513-4231"/>
-        <filter val="(809) 658-5500"/>
-        <filter val="(849) 763-2529"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A262">
     <sortCondition ref="A2:A262"/>
   </sortState>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F2BDC2-6944-47BD-A1BB-88C42A5BEE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2050DF-9554-4057-B575-53315E2518C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="425">
   <si>
     <t>Darmanethan</t>
   </si>
@@ -1306,6 +1306,12 @@
   </si>
   <si>
     <t>931 252 452</t>
+  </si>
+  <si>
+    <t>986 579 683</t>
+  </si>
+  <si>
+    <t>992 958 823</t>
   </si>
 </sst>
 </file>
@@ -1692,6 +1698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1717,7 +1724,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1732,7 +1739,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>236</v>
       </c>
@@ -1750,7 +1757,7 @@
         <v>+51 933 668 277</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1768,7 +1775,7 @@
         <v>+51 980 596 555</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1786,7 +1793,7 @@
         <v>+58 424-7086947</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -1801,7 +1808,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>235</v>
       </c>
@@ -1819,7 +1826,7 @@
         <v>+58 412-1322018</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>193</v>
       </c>
@@ -1837,7 +1844,7 @@
         <v>+56 9 7927 3083</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -1852,7 +1859,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1870,7 +1877,7 @@
         <v>+51 985 699 608</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1888,7 +1895,7 @@
         <v>+52 1 56 1007 9583</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>191</v>
       </c>
@@ -1906,7 +1913,7 @@
         <v>+52 1 81 2944 2313</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1921,7 +1928,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1936,7 +1943,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>160</v>
       </c>
@@ -1951,7 +1958,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1969,7 +1976,7 @@
         <v>+51  984 190 584</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>149</v>
       </c>
@@ -1984,7 +1991,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2002,7 +2009,7 @@
         <v>+51 984 267 160</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2020,7 +2027,7 @@
         <v>+51  912 858 811</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -2035,7 +2042,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>136</v>
       </c>
@@ -2053,7 +2060,7 @@
         <v>+51 949 647 819</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2071,7 +2078,7 @@
         <v>+34  646 20 50 99</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>228</v>
       </c>
@@ -2086,7 +2093,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>137</v>
       </c>
@@ -2104,7 +2111,7 @@
         <v>+52  1 222 102 8165</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -2122,7 +2129,7 @@
         <v>+58 416-4398466</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -2140,7 +2147,7 @@
         <v>+54 91139028131</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -2158,7 +2165,7 @@
         <v>+57 322 4761144</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -2176,7 +2183,7 @@
         <v>+52 1 771 306 4084</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>234</v>
       </c>
@@ -2194,7 +2201,7 @@
         <v>+58 412-7060529</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -2212,7 +2219,7 @@
         <v>+51 933448842</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -2227,7 +2234,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2245,7 +2252,7 @@
         <v>+51 912358537</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>179</v>
       </c>
@@ -2263,7 +2270,7 @@
         <v>+51 950 746 501</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -2281,7 +2288,7 @@
         <v>+54 9 3794 73 7373</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>119</v>
       </c>
@@ -2296,7 +2303,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>180</v>
       </c>
@@ -2314,7 +2321,7 @@
         <v>+55 71 9370-7438</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>254</v>
       </c>
@@ -2332,7 +2339,7 @@
         <v>+51 991 176 689</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -2350,7 +2357,7 @@
         <v>+34 601 36 84 69</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2365,7 +2372,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>184</v>
       </c>
@@ -2383,7 +2390,7 @@
         <v>+51  917 057 695</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -2401,7 +2408,7 @@
         <v>+34 608 39 51 22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>221</v>
       </c>
@@ -2416,7 +2423,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>117</v>
       </c>
@@ -2431,7 +2438,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -2446,7 +2453,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>198</v>
       </c>
@@ -2464,7 +2471,7 @@
         <v>+54 93854880470</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -2482,7 +2489,7 @@
         <v>+53 51162846</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>169</v>
       </c>
@@ -2497,7 +2504,7 @@
         <v xml:space="preserve">+1 </v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -2512,7 +2519,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2530,7 +2537,7 @@
         <v>+51  920 449 371</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>68</v>
       </c>
@@ -2548,7 +2555,7 @@
         <v>+51  912 209 142</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -2563,7 +2570,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -2581,7 +2588,7 @@
         <v>+505 8799 9543</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>125</v>
       </c>
@@ -2599,7 +2606,7 @@
         <v>+52 1 686 589 5829</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2617,7 +2624,7 @@
         <v>+51 992 067 030</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -2632,7 +2639,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -2647,7 +2654,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>230</v>
       </c>
@@ -2662,7 +2669,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -2680,7 +2687,7 @@
         <v>+58  412-7396859</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -2698,7 +2705,7 @@
         <v>+52 1 921 208 0809</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>100</v>
       </c>
@@ -2713,7 +2720,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>166</v>
       </c>
@@ -2731,7 +2738,7 @@
         <v>+504 3204-1711</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -2749,7 +2756,7 @@
         <v>+56 99797773</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>222</v>
       </c>
@@ -2764,7 +2771,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -2782,7 +2789,7 @@
         <v>+1 305 8902347</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>408</v>
       </c>
@@ -2800,7 +2807,7 @@
         <v>+52 1 861 128 3193</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>124</v>
       </c>
@@ -2815,7 +2822,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>176</v>
       </c>
@@ -2830,7 +2837,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>216</v>
       </c>
@@ -2848,7 +2855,7 @@
         <v>+52 8341048014</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -2866,7 +2873,7 @@
         <v>+506  8936 2350</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>159</v>
       </c>
@@ -2884,7 +2891,7 @@
         <v>+1 253 212-8032</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -2899,7 +2906,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2914,7 +2921,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>110</v>
       </c>
@@ -2929,7 +2936,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>187</v>
       </c>
@@ -2944,7 +2951,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>240</v>
       </c>
@@ -2959,7 +2966,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>31</v>
       </c>
@@ -2977,7 +2984,7 @@
         <v>+51  912 058 374</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -2992,7 +2999,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>133</v>
       </c>
@@ -3007,7 +3014,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -3022,7 +3029,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>106</v>
       </c>
@@ -3037,7 +3044,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>214</v>
       </c>
@@ -3055,7 +3062,7 @@
         <v>+593  96 083 0485</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -3070,7 +3077,7 @@
         <v xml:space="preserve">+505 </v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
@@ -3085,7 +3092,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -3103,7 +3110,7 @@
         <v>+51  983 379 394</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -3118,7 +3125,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>162</v>
       </c>
@@ -3136,7 +3143,7 @@
         <v>+51 980 679 898</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>229</v>
       </c>
@@ -3151,7 +3158,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>139</v>
       </c>
@@ -3169,7 +3176,7 @@
         <v>+53  5 6467775</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>175</v>
       </c>
@@ -3187,7 +3194,7 @@
         <v>+51 943126988</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>122</v>
       </c>
@@ -3202,7 +3209,7 @@
         <v xml:space="preserve">+593 </v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>213</v>
       </c>
@@ -3217,7 +3224,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>45</v>
       </c>
@@ -3235,7 +3242,7 @@
         <v>+54 9 3412 81-3587</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -3250,7 +3257,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>120</v>
       </c>
@@ -3268,7 +3275,7 @@
         <v>+57  302 5578252</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>205</v>
       </c>
@@ -3286,7 +3293,7 @@
         <v>+593 96 151 5565</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>243</v>
       </c>
@@ -3304,7 +3311,7 @@
         <v>+51 956 677 392</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>239</v>
       </c>
@@ -3322,7 +3329,7 @@
         <v>+54 9 11 2783 9968</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>155</v>
       </c>
@@ -3340,7 +3347,7 @@
         <v>+51 961 492 733</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>34</v>
       </c>
@@ -3358,7 +3365,7 @@
         <v>+53 5 1113536</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>140</v>
       </c>
@@ -3373,7 +3380,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>232</v>
       </c>
@@ -3388,7 +3395,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>141</v>
       </c>
@@ -3403,7 +3410,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>55</v>
       </c>
@@ -3421,7 +3428,7 @@
         <v>+1 809 658-5500</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>154</v>
       </c>
@@ -3439,7 +3446,7 @@
         <v>+58 424-1216695</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>168</v>
       </c>
@@ -3457,7 +3464,7 @@
         <v>+51 963 745 855</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>224</v>
       </c>
@@ -3475,7 +3482,7 @@
         <v>+51  960 274 071</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -3493,7 +3500,7 @@
         <v>+593 98 768 2900</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -3508,7 +3515,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>246</v>
       </c>
@@ -3526,7 +3533,7 @@
         <v>+503 7868 0662</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>242</v>
       </c>
@@ -3541,7 +3548,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>156</v>
       </c>
@@ -3559,7 +3566,7 @@
         <v>+58 414-4473628</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>43</v>
       </c>
@@ -3577,7 +3584,7 @@
         <v>+57 3054850698</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>223</v>
       </c>
@@ -3592,7 +3599,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>163</v>
       </c>
@@ -3607,7 +3614,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>56</v>
       </c>
@@ -3622,7 +3629,7 @@
         <v xml:space="preserve">+507 </v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>150</v>
       </c>
@@ -3640,7 +3647,7 @@
         <v>+58  412-1885430</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -3658,7 +3665,7 @@
         <v>+51  906 691 465</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3673,7 +3680,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>165</v>
       </c>
@@ -3691,7 +3698,7 @@
         <v>+1  787 513-4231</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>46</v>
       </c>
@@ -3709,7 +3716,7 @@
         <v>+507  6898-7574</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>209</v>
       </c>
@@ -3727,7 +3734,7 @@
         <v>+52 1 444 674 9780</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3742,7 +3749,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>21</v>
       </c>
@@ -3760,7 +3767,7 @@
         <v>+51 996 668 615</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>77</v>
       </c>
@@ -3775,7 +3782,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>249</v>
       </c>
@@ -3793,7 +3800,7 @@
         <v>+52 1 55 3845 6274</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>192</v>
       </c>
@@ -3808,7 +3815,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>253</v>
       </c>
@@ -3826,7 +3833,7 @@
         <v>+51  921 447 908</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>12</v>
       </c>
@@ -3844,7 +3851,7 @@
         <v>+51 976 413 331</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>183</v>
       </c>
@@ -3859,7 +3866,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>101</v>
       </c>
@@ -3874,7 +3881,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>157</v>
       </c>
@@ -3889,7 +3896,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>47</v>
       </c>
@@ -3904,7 +3911,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>220</v>
       </c>
@@ -3922,7 +3929,7 @@
         <v>+52 Juni Frostheart</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>257</v>
       </c>
@@ -3940,7 +3947,7 @@
         <v>+54 9 11 2526 8333</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>247</v>
       </c>
@@ -3958,7 +3965,7 @@
         <v>+51 963 347 387</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -3976,7 +3983,7 @@
         <v>+52 1 81 2684 3183</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>135</v>
       </c>
@@ -3991,7 +3998,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>178</v>
       </c>
@@ -4006,7 +4013,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>109</v>
       </c>
@@ -4021,7 +4028,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -4036,7 +4043,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>26</v>
       </c>
@@ -4054,7 +4061,7 @@
         <v>+57 302 3773516</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -4072,7 +4079,7 @@
         <v>+54  9 11 2372-2211</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>211</v>
       </c>
@@ -4090,7 +4097,7 @@
         <v>+51 960 749 072</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -4108,10 +4115,13 @@
         <v>+51 984 784 816</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>244</v>
       </c>
+      <c r="B145" t="s">
+        <v>423</v>
+      </c>
       <c r="C145" t="s">
         <v>270</v>
       </c>
@@ -4120,10 +4130,10 @@
       </c>
       <c r="E145" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">+51 </v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+        <v>+51 986 579 683</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>207</v>
       </c>
@@ -4141,7 +4151,7 @@
         <v>+52 1 614 529 6392</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>210</v>
       </c>
@@ -4159,7 +4169,7 @@
         <v>+52 1 287 154 7879</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>174</v>
       </c>
@@ -4174,7 +4184,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>185</v>
       </c>
@@ -4189,7 +4199,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>65</v>
       </c>
@@ -4207,7 +4217,7 @@
         <v>+593 98 174 5020</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -4222,7 +4232,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>118</v>
       </c>
@@ -4237,7 +4247,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>172</v>
       </c>
@@ -4255,7 +4265,7 @@
         <v>+52 1 771 297 6010</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>177</v>
       </c>
@@ -4270,7 +4280,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>188</v>
       </c>
@@ -4288,7 +4298,7 @@
         <v>+52  1 983 752 2450</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>93</v>
       </c>
@@ -4303,7 +4313,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>153</v>
       </c>
@@ -4321,7 +4331,7 @@
         <v>+58 424-6956750</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>72</v>
       </c>
@@ -4339,7 +4349,7 @@
         <v>+51  965 337 810</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>86</v>
       </c>
@@ -4354,7 +4364,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>87</v>
       </c>
@@ -4369,7 +4379,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>75</v>
       </c>
@@ -4384,7 +4394,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>200</v>
       </c>
@@ -4399,7 +4409,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>252</v>
       </c>
@@ -4417,7 +4427,7 @@
         <v>+51  945 349 568</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>251</v>
       </c>
@@ -4435,7 +4445,7 @@
         <v>+52 1 735 162 2046</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>245</v>
       </c>
@@ -4453,7 +4463,7 @@
         <v>+51 970 857 085</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>78</v>
       </c>
@@ -4468,7 +4478,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>147</v>
       </c>
@@ -4486,7 +4496,7 @@
         <v>+52  1 673 472 3074</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>59</v>
       </c>
@@ -4504,7 +4514,7 @@
         <v>+54 9 2974 22-6785</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>241</v>
       </c>
@@ -4522,7 +4532,7 @@
         <v>+52 1 55 1805 8456</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>233</v>
       </c>
@@ -4537,7 +4547,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -4555,7 +4565,7 @@
         <v>+54  9 11 6135-9811</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>201</v>
       </c>
@@ -4570,7 +4580,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>218</v>
       </c>
@@ -4588,7 +4598,7 @@
         <v>+51 991 342 085</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>69</v>
       </c>
@@ -4603,7 +4613,7 @@
         <v xml:space="preserve">+506 </v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>217</v>
       </c>
@@ -4618,7 +4628,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>167</v>
       </c>
@@ -4633,7 +4643,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>256</v>
       </c>
@@ -4651,7 +4661,7 @@
         <v>+53 5 6957902</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>134</v>
       </c>
@@ -4666,7 +4676,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>132</v>
       </c>
@@ -4681,7 +4691,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>29</v>
       </c>
@@ -4699,7 +4709,7 @@
         <v>+51 977 404 957</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>53</v>
       </c>
@@ -4717,7 +4727,7 @@
         <v>+52 1 229 229 9515</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>64</v>
       </c>
@@ -4735,7 +4745,7 @@
         <v>+51 986 824 543</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -4753,7 +4763,7 @@
         <v>+591 69865757</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>58</v>
       </c>
@@ -4771,7 +4781,7 @@
         <v>+506  7139 5493</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>115</v>
       </c>
@@ -4786,7 +4796,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>197</v>
       </c>
@@ -4804,7 +4814,7 @@
         <v>+58 424-2233503</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>206</v>
       </c>
@@ -4822,7 +4832,7 @@
         <v>+52 6644057270</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>3</v>
       </c>
@@ -4840,7 +4850,7 @@
         <v>+51 955 121 011</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>171</v>
       </c>
@@ -4855,7 +4865,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>104</v>
       </c>
@@ -4870,7 +4880,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>152</v>
       </c>
@@ -4888,7 +4898,7 @@
         <v>+52  1 479 233 6442</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>103</v>
       </c>
@@ -4903,7 +4913,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>258</v>
       </c>
@@ -4918,7 +4928,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>80</v>
       </c>
@@ -4933,7 +4943,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>189</v>
       </c>
@@ -4951,7 +4961,7 @@
         <v>+52  1 756 103 6825</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>203</v>
       </c>
@@ -4966,7 +4976,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>173</v>
       </c>
@@ -4981,7 +4991,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>202</v>
       </c>
@@ -4999,7 +5009,7 @@
         <v>+52  1 981 217 7384</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>48</v>
       </c>
@@ -5017,7 +5027,7 @@
         <v>+52 1 231 176 9718</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>248</v>
       </c>
@@ -5032,7 +5042,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -5050,7 +5060,7 @@
         <v>+52  1 55 7364 9786</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>151</v>
       </c>
@@ -5065,7 +5075,7 @@
         <v xml:space="preserve">+56 </v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>182</v>
       </c>
@@ -5080,7 +5090,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>195</v>
       </c>
@@ -5098,7 +5108,7 @@
         <v>+53 5 1795768</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>96</v>
       </c>
@@ -5113,7 +5123,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>250</v>
       </c>
@@ -5131,7 +5141,7 @@
         <v>+58 414-8694655</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>97</v>
       </c>
@@ -5146,7 +5156,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>28</v>
       </c>
@@ -5164,7 +5174,7 @@
         <v>+51 981 000 049</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>190</v>
       </c>
@@ -5179,7 +5189,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>145</v>
       </c>
@@ -5197,7 +5207,7 @@
         <v>+56 9 7878 6558</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>7</v>
       </c>
@@ -5215,7 +5225,7 @@
         <v>+51 973 614 848</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>15</v>
       </c>
@@ -5233,7 +5243,7 @@
         <v>+51 971 942 638</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>237</v>
       </c>
@@ -5248,7 +5258,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>40</v>
       </c>
@@ -5266,7 +5276,7 @@
         <v>+58 422-0376517</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>91</v>
       </c>
@@ -5281,7 +5291,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>226</v>
       </c>
@@ -5299,7 +5309,7 @@
         <v>+52  1 834 252 9665</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>14</v>
       </c>
@@ -5317,7 +5327,7 @@
         <v>+506 6082 6653</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>67</v>
       </c>
@@ -5332,7 +5342,7 @@
         <v xml:space="preserve">+503 </v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>116</v>
       </c>
@@ -5347,10 +5357,13 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>164</v>
       </c>
+      <c r="B220" s="3" t="s">
+        <v>424</v>
+      </c>
       <c r="C220" t="s">
         <v>270</v>
       </c>
@@ -5359,10 +5372,10 @@
       </c>
       <c r="E220" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">+51 </v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+        <v>+51 992 958 823</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>148</v>
       </c>
@@ -5380,7 +5393,7 @@
         <v>+58 412-5885303</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>98</v>
       </c>
@@ -5395,7 +5408,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>259</v>
       </c>
@@ -5410,7 +5423,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>79</v>
       </c>
@@ -5425,7 +5438,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>60</v>
       </c>
@@ -5443,7 +5456,7 @@
         <v>+58 414-7234994</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>158</v>
       </c>
@@ -5461,7 +5474,7 @@
         <v>+1 849 763-2529</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>196</v>
       </c>
@@ -5479,7 +5492,7 @@
         <v>+52 1 56 3172 0225</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -5494,7 +5507,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>36</v>
       </c>
@@ -5509,7 +5522,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>123</v>
       </c>
@@ -5524,7 +5537,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>73</v>
       </c>
@@ -5539,7 +5552,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>85</v>
       </c>
@@ -5554,7 +5567,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>225</v>
       </c>
@@ -5569,7 +5582,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>143</v>
       </c>
@@ -5584,7 +5597,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>219</v>
       </c>
@@ -5599,7 +5612,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>255</v>
       </c>
@@ -5617,7 +5630,7 @@
         <v>+51 923 404 224</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>81</v>
       </c>
@@ -5632,7 +5645,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>19</v>
       </c>
@@ -5650,7 +5663,7 @@
         <v>+51 987 200 136</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>13</v>
       </c>
@@ -5668,7 +5681,7 @@
         <v>+51 972691544</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>186</v>
       </c>
@@ -5686,7 +5699,7 @@
         <v>+53  5 2756474</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>204</v>
       </c>
@@ -5701,7 +5714,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>212</v>
       </c>
@@ -5716,7 +5729,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>131</v>
       </c>
@@ -5731,7 +5744,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>231</v>
       </c>
@@ -5746,7 +5759,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>76</v>
       </c>
@@ -5761,7 +5774,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>49</v>
       </c>
@@ -5776,7 +5789,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>24</v>
       </c>
@@ -5794,7 +5807,7 @@
         <v>+51 937 332 268</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>102</v>
       </c>
@@ -5812,7 +5825,7 @@
         <v>+51 955 963 610</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>170</v>
       </c>
@@ -5830,7 +5843,7 @@
         <v>+51 931 252 452</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>181</v>
       </c>
@@ -5845,7 +5858,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>82</v>
       </c>
@@ -5860,7 +5873,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1</v>
       </c>
@@ -5878,7 +5891,7 @@
         <v>+51 945 323 097</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>208</v>
       </c>
@@ -5893,7 +5906,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>63</v>
       </c>
@@ -5911,7 +5924,7 @@
         <v>+51 965 373 102</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>227</v>
       </c>
@@ -5929,7 +5942,7 @@
         <v>+52 1 916 116 9432</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>238</v>
       </c>
@@ -5947,7 +5960,7 @@
         <v>+52  1 771 112 3061</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>215</v>
       </c>
@@ -5962,7 +5975,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>70</v>
       </c>
@@ -5980,7 +5993,7 @@
         <v>+51 955 834 817</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>144</v>
       </c>
@@ -5995,7 +6008,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>95</v>
       </c>
@@ -6010,7 +6023,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
@@ -6028,7 +6041,7 @@
         <v>+54 9 3794 12-0368</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>11</v>
       </c>
@@ -6046,7 +6059,7 @@
         <v>+502 4760 5947</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>404</v>
       </c>
@@ -6064,7 +6077,7 @@
         <v>+57 333 2913156</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>406</v>
       </c>
@@ -6082,7 +6095,7 @@
         <v>+54 9 11 2507-8576</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>409</v>
       </c>
@@ -6097,7 +6110,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>410</v>
       </c>
@@ -6115,7 +6128,7 @@
         <v>+51  966 803 562</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>416</v>
       </c>
@@ -6133,7 +6146,7 @@
         <v>+58 412-8286364</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>418</v>
       </c>
@@ -6151,7 +6164,7 @@
         <v>+503 7279 9978</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>421</v>
       </c>
@@ -6169,14 +6182,16 @@
         <v>+51 964 533 667</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
     </row>
-    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
@@ -6184,7 +6199,13 @@
       <c r="F273" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
+  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Saperoko10"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A262">
     <sortCondition ref="A2:A262"/>
   </sortState>

--- a/celulares.xlsx
+++ b/celulares.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2050DF-9554-4057-B575-53315E2518C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C9D376-FFC4-48C5-A18A-B32FFF4BB5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{DED98CA9-F979-4D07-9D00-E546A9186304}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1698,7 +1698,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1724,7 +1723,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1739,7 +1738,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>236</v>
       </c>
@@ -1757,7 +1756,7 @@
         <v>+51 933 668 277</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1775,7 +1774,7 @@
         <v>+51 980 596 555</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1793,7 +1792,7 @@
         <v>+58 424-7086947</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -1808,7 +1807,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>235</v>
       </c>
@@ -1826,7 +1825,7 @@
         <v>+58 412-1322018</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>193</v>
       </c>
@@ -1844,7 +1843,7 @@
         <v>+56 9 7927 3083</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -1859,7 +1858,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1877,7 +1876,7 @@
         <v>+51 985 699 608</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1895,7 +1894,7 @@
         <v>+52 1 56 1007 9583</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>191</v>
       </c>
@@ -1913,7 +1912,7 @@
         <v>+52 1 81 2944 2313</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1928,7 +1927,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1943,7 +1942,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>160</v>
       </c>
@@ -1958,7 +1957,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1976,7 +1975,7 @@
         <v>+51  984 190 584</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>149</v>
       </c>
@@ -1991,7 +1990,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2009,7 +2008,7 @@
         <v>+51 984 267 160</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2027,7 +2026,7 @@
         <v>+51  912 858 811</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -2042,7 +2041,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>136</v>
       </c>
@@ -2060,7 +2059,7 @@
         <v>+51 949 647 819</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2078,7 +2077,7 @@
         <v>+34  646 20 50 99</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>228</v>
       </c>
@@ -2093,7 +2092,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>137</v>
       </c>
@@ -2111,7 +2110,7 @@
         <v>+52  1 222 102 8165</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -2129,7 +2128,7 @@
         <v>+58 416-4398466</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -2147,7 +2146,7 @@
         <v>+54 91139028131</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>138</v>
       </c>
@@ -2165,7 +2164,7 @@
         <v>+57 322 4761144</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>42</v>
       </c>
@@ -2183,7 +2182,7 @@
         <v>+52 1 771 306 4084</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>234</v>
       </c>
@@ -2201,7 +2200,7 @@
         <v>+58 412-7060529</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -2219,7 +2218,7 @@
         <v>+51 933448842</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -2234,7 +2233,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -2252,7 +2251,7 @@
         <v>+51 912358537</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>179</v>
       </c>
@@ -2270,7 +2269,7 @@
         <v>+51 950 746 501</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -2288,7 +2287,7 @@
         <v>+54 9 3794 73 7373</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>119</v>
       </c>
@@ -2303,7 +2302,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>180</v>
       </c>
@@ -2321,7 +2320,7 @@
         <v>+55 71 9370-7438</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>254</v>
       </c>
@@ -2339,7 +2338,7 @@
         <v>+51 991 176 689</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -2357,7 +2356,7 @@
         <v>+34 601 36 84 69</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>71</v>
       </c>
@@ -2372,7 +2371,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>184</v>
       </c>
@@ -2390,7 +2389,7 @@
         <v>+51  917 057 695</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -2408,7 +2407,7 @@
         <v>+34 608 39 51 22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>221</v>
       </c>
@@ -2423,7 +2422,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>117</v>
       </c>
@@ -2438,7 +2437,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -2453,7 +2452,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>198</v>
       </c>
@@ -2471,7 +2470,7 @@
         <v>+54 93854880470</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>61</v>
       </c>
@@ -2489,7 +2488,7 @@
         <v>+53 51162846</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>169</v>
       </c>
@@ -2504,7 +2503,7 @@
         <v xml:space="preserve">+1 </v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>57</v>
       </c>
@@ -2519,7 +2518,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>10</v>
       </c>
@@ -2537,7 +2536,7 @@
         <v>+51  920 449 371</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>68</v>
       </c>
@@ -2555,7 +2554,7 @@
         <v>+51  912 209 142</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -2570,7 +2569,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -2588,7 +2587,7 @@
         <v>+505 8799 9543</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>125</v>
       </c>
@@ -2606,7 +2605,7 @@
         <v>+52 1 686 589 5829</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2624,7 +2623,7 @@
         <v>+51 992 067 030</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>108</v>
       </c>
@@ -2639,7 +2638,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -2654,7 +2653,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>230</v>
       </c>
@@ -2669,7 +2668,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>32</v>
       </c>
@@ -2687,7 +2686,7 @@
         <v>+58  412-7396859</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -2705,7 +2704,7 @@
         <v>+52 1 921 208 0809</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>100</v>
       </c>
@@ -2720,7 +2719,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>166</v>
       </c>
@@ -2738,7 +2737,7 @@
         <v>+504 3204-1711</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>128</v>
       </c>
@@ -2756,7 +2755,7 @@
         <v>+56 99797773</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>222</v>
       </c>
@@ -2771,7 +2770,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -2789,7 +2788,7 @@
         <v>+1 305 8902347</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>408</v>
       </c>
@@ -2807,7 +2806,7 @@
         <v>+52 1 861 128 3193</v>
       </c>
     </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>124</v>
       </c>
@@ -2822,7 +2821,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>176</v>
       </c>
@@ -2837,7 +2836,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>216</v>
       </c>
@@ -2855,7 +2854,7 @@
         <v>+52 8341048014</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -2873,7 +2872,7 @@
         <v>+506  8936 2350</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>159</v>
       </c>
@@ -2891,7 +2890,7 @@
         <v>+1 253 212-8032</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -2906,7 +2905,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2921,7 +2920,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>110</v>
       </c>
@@ -2936,7 +2935,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>187</v>
       </c>
@@ -2951,7 +2950,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>240</v>
       </c>
@@ -2966,7 +2965,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>31</v>
       </c>
@@ -2984,7 +2983,7 @@
         <v>+51  912 058 374</v>
       </c>
     </row>
-    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>88</v>
       </c>
@@ -2999,7 +2998,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>133</v>
       </c>
@@ -3014,7 +3013,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>90</v>
       </c>
@@ -3029,7 +3028,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>106</v>
       </c>
@@ -3044,7 +3043,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>214</v>
       </c>
@@ -3062,7 +3061,7 @@
         <v>+593  96 083 0485</v>
       </c>
     </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -3077,7 +3076,7 @@
         <v xml:space="preserve">+505 </v>
       </c>
     </row>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
@@ -3092,7 +3091,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>44</v>
       </c>
@@ -3110,7 +3109,7 @@
         <v>+51  983 379 394</v>
       </c>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -3125,7 +3124,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>162</v>
       </c>
@@ -3143,7 +3142,7 @@
         <v>+51 980 679 898</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>229</v>
       </c>
@@ -3158,7 +3157,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>139</v>
       </c>
@@ -3176,7 +3175,7 @@
         <v>+53  5 6467775</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>175</v>
       </c>
@@ -3194,7 +3193,7 @@
         <v>+51 943126988</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>122</v>
       </c>
@@ -3209,7 +3208,7 @@
         <v xml:space="preserve">+593 </v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>213</v>
       </c>
@@ -3224,7 +3223,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>45</v>
       </c>
@@ -3242,7 +3241,7 @@
         <v>+54 9 3412 81-3587</v>
       </c>
     </row>
-    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>89</v>
       </c>
@@ -3257,7 +3256,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>120</v>
       </c>
@@ -3275,7 +3274,7 @@
         <v>+57  302 5578252</v>
       </c>
     </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>205</v>
       </c>
@@ -3293,7 +3292,7 @@
         <v>+593 96 151 5565</v>
       </c>
     </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>243</v>
       </c>
@@ -3311,7 +3310,7 @@
         <v>+51 956 677 392</v>
       </c>
     </row>
-    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>239</v>
       </c>
@@ -3329,7 +3328,7 @@
         <v>+54 9 11 2783 9968</v>
       </c>
     </row>
-    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>155</v>
       </c>
@@ -3347,7 +3346,7 @@
         <v>+51 961 492 733</v>
       </c>
     </row>
-    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>34</v>
       </c>
@@ -3365,7 +3364,7 @@
         <v>+53 5 1113536</v>
       </c>
     </row>
-    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>140</v>
       </c>
@@ -3380,7 +3379,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>232</v>
       </c>
@@ -3395,7 +3394,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>141</v>
       </c>
@@ -3410,7 +3409,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>55</v>
       </c>
@@ -3428,7 +3427,7 @@
         <v>+1 809 658-5500</v>
       </c>
     </row>
-    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>154</v>
       </c>
@@ -3446,7 +3445,7 @@
         <v>+58 424-1216695</v>
       </c>
     </row>
-    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>168</v>
       </c>
@@ -3464,7 +3463,7 @@
         <v>+51 963 745 855</v>
       </c>
     </row>
-    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>224</v>
       </c>
@@ -3482,7 +3481,7 @@
         <v>+51  960 274 071</v>
       </c>
     </row>
-    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -3500,7 +3499,7 @@
         <v>+593 98 768 2900</v>
       </c>
     </row>
-    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -3515,7 +3514,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>246</v>
       </c>
@@ -3533,7 +3532,7 @@
         <v>+503 7868 0662</v>
       </c>
     </row>
-    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>242</v>
       </c>
@@ -3548,7 +3547,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>156</v>
       </c>
@@ -3566,7 +3565,7 @@
         <v>+58 414-4473628</v>
       </c>
     </row>
-    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>43</v>
       </c>
@@ -3584,7 +3583,7 @@
         <v>+57 3054850698</v>
       </c>
     </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>223</v>
       </c>
@@ -3599,7 +3598,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>163</v>
       </c>
@@ -3614,7 +3613,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>56</v>
       </c>
@@ -3629,7 +3628,7 @@
         <v xml:space="preserve">+507 </v>
       </c>
     </row>
-    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>150</v>
       </c>
@@ -3647,7 +3646,7 @@
         <v>+58  412-1885430</v>
       </c>
     </row>
-    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -3665,7 +3664,7 @@
         <v>+51  906 691 465</v>
       </c>
     </row>
-    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3680,7 +3679,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>165</v>
       </c>
@@ -3698,7 +3697,7 @@
         <v>+1  787 513-4231</v>
       </c>
     </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>46</v>
       </c>
@@ -3716,7 +3715,7 @@
         <v>+507  6898-7574</v>
       </c>
     </row>
-    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>209</v>
       </c>
@@ -3734,7 +3733,7 @@
         <v>+52 1 444 674 9780</v>
       </c>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2</v>
       </c>
@@ -3749,7 +3748,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>21</v>
       </c>
@@ -3767,7 +3766,7 @@
         <v>+51 996 668 615</v>
       </c>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>77</v>
       </c>
@@ -3782,7 +3781,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>249</v>
       </c>
@@ -3800,7 +3799,7 @@
         <v>+52 1 55 3845 6274</v>
       </c>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>192</v>
       </c>
@@ -3815,7 +3814,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>253</v>
       </c>
@@ -3833,7 +3832,7 @@
         <v>+51  921 447 908</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>12</v>
       </c>
@@ -3851,7 +3850,7 @@
         <v>+51 976 413 331</v>
       </c>
     </row>
-    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>183</v>
       </c>
@@ -3866,7 +3865,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>101</v>
       </c>
@@ -3881,7 +3880,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>157</v>
       </c>
@@ -3896,7 +3895,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>47</v>
       </c>
@@ -3911,7 +3910,7 @@
         <v xml:space="preserve">+57 </v>
       </c>
     </row>
-    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>220</v>
       </c>
@@ -3929,7 +3928,7 @@
         <v>+52 Juni Frostheart</v>
       </c>
     </row>
-    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>257</v>
       </c>
@@ -3947,7 +3946,7 @@
         <v>+54 9 11 2526 8333</v>
       </c>
     </row>
-    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>247</v>
       </c>
@@ -3965,7 +3964,7 @@
         <v>+51 963 347 387</v>
       </c>
     </row>
-    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -3983,7 +3982,7 @@
         <v>+52 1 81 2684 3183</v>
       </c>
     </row>
-    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>135</v>
       </c>
@@ -3998,7 +3997,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>178</v>
       </c>
@@ -4013,7 +4012,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>109</v>
       </c>
@@ -4028,7 +4027,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -4043,7 +4042,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>26</v>
       </c>
@@ -4061,7 +4060,7 @@
         <v>+57 302 3773516</v>
       </c>
     </row>
-    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -4079,7 +4078,7 @@
         <v>+54  9 11 2372-2211</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>211</v>
       </c>
@@ -4097,7 +4096,7 @@
         <v>+51 960 749 072</v>
       </c>
     </row>
-    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -4115,7 +4114,7 @@
         <v>+51 984 784 816</v>
       </c>
     </row>
-    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>244</v>
       </c>
@@ -4133,7 +4132,7 @@
         <v>+51 986 579 683</v>
       </c>
     </row>
-    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>207</v>
       </c>
@@ -4151,7 +4150,7 @@
         <v>+52 1 614 529 6392</v>
       </c>
     </row>
-    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>210</v>
       </c>
@@ -4169,7 +4168,7 @@
         <v>+52 1 287 154 7879</v>
       </c>
     </row>
-    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>174</v>
       </c>
@@ -4184,7 +4183,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>185</v>
       </c>
@@ -4199,7 +4198,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>65</v>
       </c>
@@ -4217,7 +4216,7 @@
         <v>+593 98 174 5020</v>
       </c>
     </row>
-    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -4232,7 +4231,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>118</v>
       </c>
@@ -4247,7 +4246,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>172</v>
       </c>
@@ -4265,7 +4264,7 @@
         <v>+52 1 771 297 6010</v>
       </c>
     </row>
-    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>177</v>
       </c>
@@ -4280,7 +4279,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>188</v>
       </c>
@@ -4298,7 +4297,7 @@
         <v>+52  1 983 752 2450</v>
       </c>
     </row>
-    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>93</v>
       </c>
@@ -4313,7 +4312,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>153</v>
       </c>
@@ -4331,7 +4330,7 @@
         <v>+58 424-6956750</v>
       </c>
     </row>
-    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>72</v>
       </c>
@@ -4349,7 +4348,7 @@
         <v>+51  965 337 810</v>
       </c>
     </row>
-    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>86</v>
       </c>
@@ -4364,7 +4363,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>87</v>
       </c>
@@ -4379,7 +4378,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>75</v>
       </c>
@@ -4394,7 +4393,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>200</v>
       </c>
@@ -4409,7 +4408,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>252</v>
       </c>
@@ -4427,7 +4426,7 @@
         <v>+51  945 349 568</v>
       </c>
     </row>
-    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>251</v>
       </c>
@@ -4445,7 +4444,7 @@
         <v>+52 1 735 162 2046</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>245</v>
       </c>
@@ -4463,7 +4462,7 @@
         <v>+51 970 857 085</v>
       </c>
     </row>
-    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>78</v>
       </c>
@@ -4478,7 +4477,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>147</v>
       </c>
@@ -4496,7 +4495,7 @@
         <v>+52  1 673 472 3074</v>
       </c>
     </row>
-    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>59</v>
       </c>
@@ -4514,7 +4513,7 @@
         <v>+54 9 2974 22-6785</v>
       </c>
     </row>
-    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>241</v>
       </c>
@@ -4532,7 +4531,7 @@
         <v>+52 1 55 1805 8456</v>
       </c>
     </row>
-    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>233</v>
       </c>
@@ -4547,7 +4546,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -4565,7 +4564,7 @@
         <v>+54  9 11 6135-9811</v>
       </c>
     </row>
-    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>201</v>
       </c>
@@ -4580,7 +4579,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="173" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>218</v>
       </c>
@@ -4598,7 +4597,7 @@
         <v>+51 991 342 085</v>
       </c>
     </row>
-    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>69</v>
       </c>
@@ -4613,7 +4612,7 @@
         <v xml:space="preserve">+506 </v>
       </c>
     </row>
-    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>217</v>
       </c>
@@ -4628,7 +4627,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>167</v>
       </c>
@@ -4643,7 +4642,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>256</v>
       </c>
@@ -4661,7 +4660,7 @@
         <v>+53 5 6957902</v>
       </c>
     </row>
-    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>134</v>
       </c>
@@ -4676,7 +4675,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>132</v>
       </c>
@@ -4691,7 +4690,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="180" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>29</v>
       </c>
@@ -4709,7 +4708,7 @@
         <v>+51 977 404 957</v>
       </c>
     </row>
-    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>53</v>
       </c>
@@ -4727,7 +4726,7 @@
         <v>+52 1 229 229 9515</v>
       </c>
     </row>
-    <row r="182" spans="1:5" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>64</v>
       </c>
@@ -4745,7 +4744,7 @@
         <v>+51 986 824 543</v>
       </c>
     </row>
-    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -4763,7 +4762,7 @@
         <v>+591 69865757</v>
       </c>
     </row>
-    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>58</v>
       </c>
@@ -4781,7 +4780,7 @@
         <v>+506  7139 5493</v>
       </c>
     </row>
-    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>115</v>
       </c>
@@ -4796,7 +4795,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>197</v>
       </c>
@@ -4814,7 +4813,7 @@
         <v>+58 424-2233503</v>
       </c>
     </row>
-    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>206</v>
       </c>
@@ -4832,7 +4831,7 @@
         <v>+52 6644057270</v>
       </c>
     </row>
-    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>3</v>
       </c>
@@ -4850,7 +4849,7 @@
         <v>+51 955 121 011</v>
       </c>
     </row>
-    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>171</v>
       </c>
@@ -4865,7 +4864,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>104</v>
       </c>
@@ -4880,7 +4879,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>152</v>
       </c>
@@ -4898,7 +4897,7 @@
         <v>+52  1 479 233 6442</v>
       </c>
     </row>
-    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>103</v>
       </c>
@@ -4913,7 +4912,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>258</v>
       </c>
@@ -4928,7 +4927,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>80</v>
       </c>
@@ -4943,7 +4942,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>189</v>
       </c>
@@ -4961,7 +4960,7 @@
         <v>+52  1 756 103 6825</v>
       </c>
     </row>
-    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>203</v>
       </c>
@@ -4976,7 +4975,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>173</v>
       </c>
@@ -4991,7 +4990,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>202</v>
       </c>
@@ -5009,7 +5008,7 @@
         <v>+52  1 981 217 7384</v>
       </c>
     </row>
-    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>48</v>
       </c>
@@ -5027,7 +5026,7 @@
         <v>+52 1 231 176 9718</v>
       </c>
     </row>
-    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>248</v>
       </c>
@@ -5042,7 +5041,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -5060,7 +5059,7 @@
         <v>+52  1 55 7364 9786</v>
       </c>
     </row>
-    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>151</v>
       </c>
@@ -5075,7 +5074,7 @@
         <v xml:space="preserve">+56 </v>
       </c>
     </row>
-    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>182</v>
       </c>
@@ -5090,7 +5089,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>195</v>
       </c>
@@ -5108,7 +5107,7 @@
         <v>+53 5 1795768</v>
       </c>
     </row>
-    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>96</v>
       </c>
@@ -5123,7 +5122,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>250</v>
       </c>
@@ -5141,7 +5140,7 @@
         <v>+58 414-8694655</v>
       </c>
     </row>
-    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>97</v>
       </c>
@@ -5156,7 +5155,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>28</v>
       </c>
@@ -5174,7 +5173,7 @@
         <v>+51 981 000 049</v>
       </c>
     </row>
-    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>190</v>
       </c>
@@ -5189,7 +5188,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>145</v>
       </c>
@@ -5207,7 +5206,7 @@
         <v>+56 9 7878 6558</v>
       </c>
     </row>
-    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>7</v>
       </c>
@@ -5225,7 +5224,7 @@
         <v>+51 973 614 848</v>
       </c>
     </row>
-    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>15</v>
       </c>
@@ -5243,7 +5242,7 @@
         <v>+51 971 942 638</v>
       </c>
     </row>
-    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>237</v>
       </c>
@@ -5258,7 +5257,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>40</v>
       </c>
@@ -5276,7 +5275,7 @@
         <v>+58 422-0376517</v>
       </c>
     </row>
-    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>91</v>
       </c>
@@ -5291,7 +5290,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>226</v>
       </c>
@@ -5309,7 +5308,7 @@
         <v>+52  1 834 252 9665</v>
       </c>
     </row>
-    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>14</v>
       </c>
@@ -5327,7 +5326,7 @@
         <v>+506 6082 6653</v>
       </c>
     </row>
-    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>67</v>
       </c>
@@ -5342,7 +5341,7 @@
         <v xml:space="preserve">+503 </v>
       </c>
     </row>
-    <row r="219" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>116</v>
       </c>
@@ -5375,7 +5374,7 @@
         <v>+51 992 958 823</v>
       </c>
     </row>
-    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>148</v>
       </c>
@@ -5393,7 +5392,7 @@
         <v>+58 412-5885303</v>
       </c>
     </row>
-    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>98</v>
       </c>
@@ -5408,7 +5407,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>259</v>
       </c>
@@ -5423,7 +5422,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>79</v>
       </c>
@@ -5438,7 +5437,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>60</v>
       </c>
@@ -5456,7 +5455,7 @@
         <v>+58 414-7234994</v>
       </c>
     </row>
-    <row r="226" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>158</v>
       </c>
@@ -5474,7 +5473,7 @@
         <v>+1 849 763-2529</v>
       </c>
     </row>
-    <row r="227" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>196</v>
       </c>
@@ -5492,7 +5491,7 @@
         <v>+52 1 56 3172 0225</v>
       </c>
     </row>
-    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
@@ -5507,7 +5506,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>36</v>
       </c>
@@ -5522,7 +5521,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="230" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>123</v>
       </c>
@@ -5537,7 +5536,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="231" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>73</v>
       </c>
@@ -5552,7 +5551,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>85</v>
       </c>
@@ -5567,7 +5566,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>225</v>
       </c>
@@ -5582,7 +5581,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>143</v>
       </c>
@@ -5597,7 +5596,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>219</v>
       </c>
@@ -5612,7 +5611,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>255</v>
       </c>
@@ -5630,7 +5629,7 @@
         <v>+51 923 404 224</v>
       </c>
     </row>
-    <row r="237" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>81</v>
       </c>
@@ -5645,7 +5644,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>19</v>
       </c>
@@ -5663,7 +5662,7 @@
         <v>+51 987 200 136</v>
       </c>
     </row>
-    <row r="239" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>13</v>
       </c>
@@ -5681,7 +5680,7 @@
         <v>+51 972691544</v>
       </c>
     </row>
-    <row r="240" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>186</v>
       </c>
@@ -5699,7 +5698,7 @@
         <v>+53  5 2756474</v>
       </c>
     </row>
-    <row r="241" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>204</v>
       </c>
@@ -5714,7 +5713,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="242" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>212</v>
       </c>
@@ -5729,7 +5728,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="243" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>131</v>
       </c>
@@ -5744,7 +5743,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>231</v>
       </c>
@@ -5759,7 +5758,7 @@
         <v xml:space="preserve">+54 </v>
       </c>
     </row>
-    <row r="245" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>76</v>
       </c>
@@ -5774,7 +5773,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="246" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>49</v>
       </c>
@@ -5789,7 +5788,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="247" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>24</v>
       </c>
@@ -5807,7 +5806,7 @@
         <v>+51 937 332 268</v>
       </c>
     </row>
-    <row r="248" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>102</v>
       </c>
@@ -5825,7 +5824,7 @@
         <v>+51 955 963 610</v>
       </c>
     </row>
-    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>170</v>
       </c>
@@ -5843,7 +5842,7 @@
         <v>+51 931 252 452</v>
       </c>
     </row>
-    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>181</v>
       </c>
@@ -5858,7 +5857,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>82</v>
       </c>
@@ -5873,7 +5872,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="252" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1</v>
       </c>
@@ -5891,7 +5890,7 @@
         <v>+51 945 323 097</v>
       </c>
     </row>
-    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>208</v>
       </c>
@@ -5906,7 +5905,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>63</v>
       </c>
@@ -5924,7 +5923,7 @@
         <v>+51 965 373 102</v>
       </c>
     </row>
-    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>227</v>
       </c>
@@ -5942,7 +5941,7 @@
         <v>+52 1 916 116 9432</v>
       </c>
     </row>
-    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>238</v>
       </c>
@@ -5960,7 +5959,7 @@
         <v>+52  1 771 112 3061</v>
       </c>
     </row>
-    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>215</v>
       </c>
@@ -5975,7 +5974,7 @@
         <v xml:space="preserve">+58 </v>
       </c>
     </row>
-    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>70</v>
       </c>
@@ -5993,7 +5992,7 @@
         <v>+51 955 834 817</v>
       </c>
     </row>
-    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>144</v>
       </c>
@@ -6008,7 +6007,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>95</v>
       </c>
@@ -6023,7 +6022,7 @@
         <v xml:space="preserve">+52 </v>
       </c>
     </row>
-    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>62</v>
       </c>
@@ -6041,7 +6040,7 @@
         <v>+54 9 3794 12-0368</v>
       </c>
     </row>
-    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>11</v>
       </c>
@@ -6059,7 +6058,7 @@
         <v>+502 4760 5947</v>
       </c>
     </row>
-    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>404</v>
       </c>
@@ -6077,7 +6076,7 @@
         <v>+57 333 2913156</v>
       </c>
     </row>
-    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>406</v>
       </c>
@@ -6095,7 +6094,7 @@
         <v>+54 9 11 2507-8576</v>
       </c>
     </row>
-    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>409</v>
       </c>
@@ -6110,7 +6109,7 @@
         <v xml:space="preserve">+51 </v>
       </c>
     </row>
-    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>410</v>
       </c>
@@ -6128,7 +6127,7 @@
         <v>+51  966 803 562</v>
       </c>
     </row>
-    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>416</v>
       </c>
@@ -6146,7 +6145,7 @@
         <v>+58 412-8286364</v>
       </c>
     </row>
-    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>418</v>
       </c>
@@ -6164,7 +6163,7 @@
         <v>+503 7279 9978</v>
       </c>
     </row>
-    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>421</v>
       </c>
@@ -6182,16 +6181,14 @@
         <v>+51 964 533 667</v>
       </c>
     </row>
-    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
     </row>
-    <row r="273" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
@@ -6199,13 +6196,7 @@
       <c r="F273" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Saperoko10"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E273" xr:uid="{F19E53EA-36ED-411D-8D0C-6795572AAB06}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A262">
     <sortCondition ref="A2:A262"/>
   </sortState>
